--- a/DossierConception/Dossier de test/Plan de test.xlsx
+++ b/DossierConception/Dossier de test/Plan de test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://afpadijon-my.sharepoint.com/personal/thomas_seiwert_afpa_training/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="8_{EE5D796C-EAF5-4486-9FE1-9A3EDEC21303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A97F40D-7780-4751-9B4A-8E499AE0B600}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="8_{EE5D796C-EAF5-4486-9FE1-9A3EDEC21303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4719DBF-4577-4E15-95C9-715AB88D7E5E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B55DF1D4-CED2-4AA7-A7C3-CF8CE171E57D}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="128">
   <si>
     <t>Date</t>
   </si>
@@ -385,13 +383,58 @@
     <t xml:space="preserve">Test de bout en bout réussi : Web → Service → Repository → API → BDD fonctionnent correctement.
 Objet récupéré: Representation@42526e5
 </t>
+  </si>
+  <si>
+    <t>Guitare et piano</t>
+  </si>
+  <si>
+    <t>15/04/2026 11h12</t>
+  </si>
+  <si>
+    <t>Test manuel de vérification de la liste des instruments sur la page web par rapport à la BDD</t>
+  </si>
+  <si>
+    <t>15/04/2026 11h16</t>
+  </si>
+  <si>
+    <t>Test manuel de création d'un instrument sur la page web et vérification dans la BDD</t>
+  </si>
+  <si>
+    <t>Ajout du violon dans la BDD</t>
+  </si>
+  <si>
+    <t>Violon ajouté dans la BDD</t>
+  </si>
+  <si>
+    <t>15/04/2026 11h17</t>
+  </si>
+  <si>
+    <t>Test manuel de modification d'un instrument sur la page web et vérification dans la BDD</t>
+  </si>
+  <si>
+    <t>Modification du violon en flute dans la BDD</t>
+  </si>
+  <si>
+    <t>Violon modifié en flute dans la BDD</t>
+  </si>
+  <si>
+    <t>15/04/2026 11h19</t>
+  </si>
+  <si>
+    <t>Test manuel de suppression d'un instrument sur la page web et vérification dans la BDD</t>
+  </si>
+  <si>
+    <t>Suppression de la flute dans la BDD</t>
+  </si>
+  <si>
+    <t>Flute supprimée dans la BDD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,13 +791,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -771,6 +807,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -815,7 +858,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2188A46B-E03B-44C2-AE15-50E2D24B12FA}" name="Tableau2" displayName="Tableau2" ref="A1:G37" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2188A46B-E03B-44C2-AE15-50E2D24B12FA}" name="Tableau2" displayName="Tableau2" ref="A1:G37" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G37" xr:uid="{2188A46B-E03B-44C2-AE15-50E2D24B12FA}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{2DB781ED-8675-4C4E-A396-7FC27413704D}" name="Date" dataDxfId="6"/>
@@ -831,7 +874,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1128,17 +1171,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62CEB04-8594-4AED-BC58-93479FCAB506}">
   <dimension ref="A1:G742"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.7109375" style="15" customWidth="1"/>
-    <col min="4" max="5" width="48.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="48.5703125" style="15" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="45.7109375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="28.5" customHeight="1">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="76.5">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="3" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
@@ -1205,7 +1248,7 @@
       </c>
       <c r="G3" s="17"/>
     </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="45.75">
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
@@ -1228,7 +1271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="45.75">
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
@@ -1251,7 +1294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="45.75">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
@@ -1274,7 +1317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" ht="45.75">
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
@@ -1297,7 +1340,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="8" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
@@ -1318,7 +1361,7 @@
       </c>
       <c r="G8" s="17"/>
     </row>
-    <row r="9" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="9" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -1339,7 +1382,7 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="10" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>39</v>
       </c>
@@ -1362,7 +1405,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="11" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>43</v>
       </c>
@@ -1383,7 +1426,7 @@
       </c>
       <c r="G11" s="17"/>
     </row>
-    <row r="12" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="12" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
@@ -1404,7 +1447,7 @@
       </c>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="13" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
@@ -1425,7 +1468,7 @@
       </c>
       <c r="G13" s="17"/>
     </row>
-    <row r="14" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="14" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>49</v>
       </c>
@@ -1448,7 +1491,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="3" customFormat="1">
+    <row r="15" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>54</v>
       </c>
@@ -1471,7 +1514,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="16" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>61</v>
       </c>
@@ -1494,7 +1537,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="3" customFormat="1" ht="45.75">
+    <row r="17" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>66</v>
       </c>
@@ -1517,7 +1560,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="3" customFormat="1">
+    <row r="18" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -1540,7 +1583,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="19" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>75</v>
       </c>
@@ -1563,7 +1606,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="3" customFormat="1" ht="162" customHeight="1">
+    <row r="20" spans="1:7" s="3" customFormat="1" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>79</v>
       </c>
@@ -1586,7 +1629,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="3" customFormat="1" ht="167.25">
+    <row r="21" spans="1:7" s="3" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>83</v>
       </c>
@@ -1609,7 +1652,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="3" customFormat="1" ht="167.25">
+    <row r="22" spans="1:7" s="3" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>87</v>
       </c>
@@ -1632,7 +1675,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="3" customFormat="1" ht="167.25">
+    <row r="23" spans="1:7" s="3" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>91</v>
       </c>
@@ -1655,7 +1698,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="24" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>94</v>
       </c>
@@ -1678,7 +1721,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="25" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>98</v>
       </c>
@@ -1701,7 +1744,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="3" customFormat="1" ht="30.75">
+    <row r="26" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>102</v>
       </c>
@@ -1724,7 +1767,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="3" customFormat="1" ht="45.75">
+    <row r="27" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>106</v>
       </c>
@@ -1747,7 +1790,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="3" customFormat="1" ht="69.75" customHeight="1">
+    <row r="28" spans="1:7" s="3" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>106</v>
       </c>
@@ -1770,43 +1813,91 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="3" customFormat="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="1:7" s="3" customFormat="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="4"/>
+    <row r="30" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G30" s="17"/>
     </row>
-    <row r="31" spans="1:7" s="3" customFormat="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="4"/>
+    <row r="31" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G31" s="17"/>
     </row>
-    <row r="32" spans="1:7" s="3" customFormat="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="4"/>
+    <row r="32" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="1:7" s="3" customFormat="1">
+    <row r="33" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="4"/>
       <c r="C33" s="10"/>
@@ -1815,7 +1906,7 @@
       <c r="F33" s="4"/>
       <c r="G33" s="17"/>
     </row>
-    <row r="34" spans="1:7" s="3" customFormat="1">
+    <row r="34" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="4"/>
       <c r="C34" s="10"/>
@@ -1824,7 +1915,7 @@
       <c r="F34" s="4"/>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" spans="1:7" s="3" customFormat="1">
+    <row r="35" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="4"/>
       <c r="C35" s="10"/>
@@ -1833,7 +1924,7 @@
       <c r="F35" s="4"/>
       <c r="G35" s="17"/>
     </row>
-    <row r="36" spans="1:7" s="3" customFormat="1">
+    <row r="36" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="4"/>
       <c r="C36" s="10"/>
@@ -1842,7 +1933,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="17"/>
     </row>
-    <row r="37" spans="1:7" s="3" customFormat="1">
+    <row r="37" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="13"/>
@@ -1851,7 +1942,7 @@
       <c r="F37" s="9"/>
       <c r="G37" s="18"/>
     </row>
-    <row r="38" spans="1:7" s="3" customFormat="1">
+    <row r="38" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="14"/>
@@ -1860,7 +1951,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="14"/>
     </row>
-    <row r="39" spans="1:7" s="3" customFormat="1">
+    <row r="39" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="14"/>
@@ -1869,7 +1960,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="14"/>
     </row>
-    <row r="40" spans="1:7" s="3" customFormat="1">
+    <row r="40" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="14"/>
@@ -1878,7 +1969,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" s="3" customFormat="1">
+    <row r="41" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="14"/>
@@ -1887,7 +1978,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" s="3" customFormat="1">
+    <row r="42" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="14"/>
@@ -1896,7 +1987,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="14"/>
     </row>
-    <row r="43" spans="1:7" s="3" customFormat="1">
+    <row r="43" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="14"/>
@@ -1905,7 +1996,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="14"/>
     </row>
-    <row r="44" spans="1:7" s="3" customFormat="1">
+    <row r="44" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="14"/>
@@ -1914,7 +2005,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="14"/>
     </row>
-    <row r="45" spans="1:7" s="3" customFormat="1">
+    <row r="45" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="14"/>
@@ -1923,7 +2014,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="14"/>
     </row>
-    <row r="46" spans="1:7" s="3" customFormat="1">
+    <row r="46" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="14"/>
@@ -1932,7 +2023,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="14"/>
     </row>
-    <row r="47" spans="1:7" s="3" customFormat="1">
+    <row r="47" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="14"/>
@@ -1941,7 +2032,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="14"/>
     </row>
-    <row r="48" spans="1:7" s="3" customFormat="1">
+    <row r="48" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="14"/>
@@ -1950,7 +2041,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="14"/>
     </row>
-    <row r="49" spans="1:7" s="3" customFormat="1">
+    <row r="49" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="14"/>
@@ -1959,7 +2050,7 @@
       <c r="F49" s="2"/>
       <c r="G49" s="14"/>
     </row>
-    <row r="50" spans="1:7" s="3" customFormat="1">
+    <row r="50" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="14"/>
@@ -1968,7 +2059,7 @@
       <c r="F50" s="2"/>
       <c r="G50" s="14"/>
     </row>
-    <row r="51" spans="1:7" s="3" customFormat="1">
+    <row r="51" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="14"/>
@@ -1977,7 +2068,7 @@
       <c r="F51" s="2"/>
       <c r="G51" s="14"/>
     </row>
-    <row r="52" spans="1:7" s="3" customFormat="1">
+    <row r="52" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="14"/>
@@ -1986,7 +2077,7 @@
       <c r="F52" s="2"/>
       <c r="G52" s="14"/>
     </row>
-    <row r="53" spans="1:7" s="3" customFormat="1">
+    <row r="53" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="14"/>
@@ -1995,7 +2086,7 @@
       <c r="F53" s="2"/>
       <c r="G53" s="14"/>
     </row>
-    <row r="54" spans="1:7" s="3" customFormat="1">
+    <row r="54" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="14"/>
@@ -2004,7 +2095,7 @@
       <c r="F54" s="2"/>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" spans="1:7" s="3" customFormat="1">
+    <row r="55" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="14"/>
@@ -2013,7 +2104,7 @@
       <c r="F55" s="2"/>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" s="3" customFormat="1">
+    <row r="56" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="14"/>
@@ -2022,7 +2113,7 @@
       <c r="F56" s="2"/>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" s="3" customFormat="1">
+    <row r="57" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="14"/>
@@ -2031,7 +2122,7 @@
       <c r="F57" s="2"/>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" spans="1:7" s="3" customFormat="1">
+    <row r="58" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="14"/>
@@ -2040,7 +2131,7 @@
       <c r="F58" s="2"/>
       <c r="G58" s="14"/>
     </row>
-    <row r="59" spans="1:7" s="3" customFormat="1">
+    <row r="59" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="14"/>
@@ -2049,7 +2140,7 @@
       <c r="F59" s="2"/>
       <c r="G59" s="14"/>
     </row>
-    <row r="60" spans="1:7" s="3" customFormat="1">
+    <row r="60" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="14"/>
@@ -2058,7 +2149,7 @@
       <c r="F60" s="2"/>
       <c r="G60" s="14"/>
     </row>
-    <row r="61" spans="1:7" s="3" customFormat="1">
+    <row r="61" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="14"/>
@@ -2067,7 +2158,7 @@
       <c r="F61" s="2"/>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" spans="1:7" s="3" customFormat="1">
+    <row r="62" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="14"/>
@@ -2076,7 +2167,7 @@
       <c r="F62" s="2"/>
       <c r="G62" s="14"/>
     </row>
-    <row r="63" spans="1:7" s="3" customFormat="1">
+    <row r="63" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="14"/>
@@ -2085,7 +2176,7 @@
       <c r="F63" s="2"/>
       <c r="G63" s="14"/>
     </row>
-    <row r="64" spans="1:7" s="3" customFormat="1">
+    <row r="64" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="14"/>
@@ -2094,7 +2185,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="14"/>
     </row>
-    <row r="65" spans="1:7" s="3" customFormat="1">
+    <row r="65" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="14"/>
@@ -2103,7 +2194,7 @@
       <c r="F65" s="2"/>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" spans="1:7" s="3" customFormat="1">
+    <row r="66" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="14"/>
@@ -2112,7 +2203,7 @@
       <c r="F66" s="2"/>
       <c r="G66" s="14"/>
     </row>
-    <row r="67" spans="1:7" s="3" customFormat="1">
+    <row r="67" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="14"/>
@@ -2121,7 +2212,7 @@
       <c r="F67" s="2"/>
       <c r="G67" s="14"/>
     </row>
-    <row r="68" spans="1:7" s="3" customFormat="1">
+    <row r="68" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="14"/>
@@ -2130,7 +2221,7 @@
       <c r="F68" s="2"/>
       <c r="G68" s="14"/>
     </row>
-    <row r="69" spans="1:7" s="3" customFormat="1">
+    <row r="69" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="14"/>
@@ -2139,7 +2230,7 @@
       <c r="F69" s="2"/>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" spans="1:7" s="3" customFormat="1">
+    <row r="70" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="14"/>
@@ -2148,7 +2239,7 @@
       <c r="F70" s="2"/>
       <c r="G70" s="14"/>
     </row>
-    <row r="71" spans="1:7" s="3" customFormat="1">
+    <row r="71" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="14"/>
@@ -2157,7 +2248,7 @@
       <c r="F71" s="2"/>
       <c r="G71" s="14"/>
     </row>
-    <row r="72" spans="1:7" s="3" customFormat="1">
+    <row r="72" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="14"/>
@@ -2166,7 +2257,7 @@
       <c r="F72" s="2"/>
       <c r="G72" s="14"/>
     </row>
-    <row r="73" spans="1:7" s="3" customFormat="1">
+    <row r="73" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="14"/>
@@ -2175,7 +2266,7 @@
       <c r="F73" s="2"/>
       <c r="G73" s="14"/>
     </row>
-    <row r="74" spans="1:7" s="3" customFormat="1">
+    <row r="74" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="14"/>
@@ -2184,7 +2275,7 @@
       <c r="F74" s="2"/>
       <c r="G74" s="14"/>
     </row>
-    <row r="75" spans="1:7" s="3" customFormat="1">
+    <row r="75" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="14"/>
@@ -2193,7 +2284,7 @@
       <c r="F75" s="2"/>
       <c r="G75" s="14"/>
     </row>
-    <row r="76" spans="1:7" s="3" customFormat="1">
+    <row r="76" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="14"/>
@@ -2202,7 +2293,7 @@
       <c r="F76" s="2"/>
       <c r="G76" s="14"/>
     </row>
-    <row r="77" spans="1:7" s="3" customFormat="1">
+    <row r="77" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="14"/>
@@ -2211,7 +2302,7 @@
       <c r="F77" s="2"/>
       <c r="G77" s="14"/>
     </row>
-    <row r="78" spans="1:7" s="3" customFormat="1">
+    <row r="78" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="14"/>
@@ -2220,7 +2311,7 @@
       <c r="F78" s="2"/>
       <c r="G78" s="14"/>
     </row>
-    <row r="79" spans="1:7" s="3" customFormat="1">
+    <row r="79" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="14"/>
@@ -2229,7 +2320,7 @@
       <c r="F79" s="2"/>
       <c r="G79" s="14"/>
     </row>
-    <row r="80" spans="1:7" s="3" customFormat="1">
+    <row r="80" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="14"/>
@@ -2238,7 +2329,7 @@
       <c r="F80" s="2"/>
       <c r="G80" s="14"/>
     </row>
-    <row r="81" spans="1:7" s="3" customFormat="1">
+    <row r="81" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="14"/>
@@ -2247,7 +2338,7 @@
       <c r="F81" s="2"/>
       <c r="G81" s="14"/>
     </row>
-    <row r="82" spans="1:7" s="3" customFormat="1">
+    <row r="82" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="14"/>
@@ -2256,7 +2347,7 @@
       <c r="F82" s="2"/>
       <c r="G82" s="14"/>
     </row>
-    <row r="83" spans="1:7" s="3" customFormat="1">
+    <row r="83" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="14"/>
@@ -2265,7 +2356,7 @@
       <c r="F83" s="2"/>
       <c r="G83" s="14"/>
     </row>
-    <row r="84" spans="1:7" s="3" customFormat="1">
+    <row r="84" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="14"/>
@@ -2274,7 +2365,7 @@
       <c r="F84" s="2"/>
       <c r="G84" s="14"/>
     </row>
-    <row r="85" spans="1:7" s="3" customFormat="1">
+    <row r="85" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="14"/>
@@ -2283,7 +2374,7 @@
       <c r="F85" s="2"/>
       <c r="G85" s="14"/>
     </row>
-    <row r="86" spans="1:7" s="3" customFormat="1">
+    <row r="86" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="14"/>
@@ -2292,7 +2383,7 @@
       <c r="F86" s="2"/>
       <c r="G86" s="14"/>
     </row>
-    <row r="87" spans="1:7" s="3" customFormat="1">
+    <row r="87" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="14"/>
@@ -2301,7 +2392,7 @@
       <c r="F87" s="2"/>
       <c r="G87" s="14"/>
     </row>
-    <row r="88" spans="1:7" s="3" customFormat="1">
+    <row r="88" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="14"/>
@@ -2310,7 +2401,7 @@
       <c r="F88" s="2"/>
       <c r="G88" s="14"/>
     </row>
-    <row r="89" spans="1:7" s="3" customFormat="1">
+    <row r="89" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="14"/>
@@ -2319,7 +2410,7 @@
       <c r="F89" s="2"/>
       <c r="G89" s="14"/>
     </row>
-    <row r="90" spans="1:7" s="3" customFormat="1">
+    <row r="90" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="14"/>
@@ -2328,7 +2419,7 @@
       <c r="F90" s="2"/>
       <c r="G90" s="14"/>
     </row>
-    <row r="91" spans="1:7" s="3" customFormat="1">
+    <row r="91" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="14"/>
@@ -2337,7 +2428,7 @@
       <c r="F91" s="2"/>
       <c r="G91" s="14"/>
     </row>
-    <row r="92" spans="1:7" s="3" customFormat="1">
+    <row r="92" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="14"/>
@@ -2346,7 +2437,7 @@
       <c r="F92" s="2"/>
       <c r="G92" s="14"/>
     </row>
-    <row r="93" spans="1:7" s="3" customFormat="1">
+    <row r="93" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="14"/>
@@ -2355,7 +2446,7 @@
       <c r="F93" s="2"/>
       <c r="G93" s="14"/>
     </row>
-    <row r="94" spans="1:7" s="3" customFormat="1">
+    <row r="94" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="14"/>
@@ -2364,7 +2455,7 @@
       <c r="F94" s="2"/>
       <c r="G94" s="14"/>
     </row>
-    <row r="95" spans="1:7" s="3" customFormat="1">
+    <row r="95" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="14"/>
@@ -2373,7 +2464,7 @@
       <c r="F95" s="2"/>
       <c r="G95" s="14"/>
     </row>
-    <row r="96" spans="1:7" s="3" customFormat="1">
+    <row r="96" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="14"/>
@@ -2382,7 +2473,7 @@
       <c r="F96" s="2"/>
       <c r="G96" s="14"/>
     </row>
-    <row r="97" spans="1:7" s="3" customFormat="1">
+    <row r="97" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="14"/>
@@ -2391,7 +2482,7 @@
       <c r="F97" s="2"/>
       <c r="G97" s="14"/>
     </row>
-    <row r="98" spans="1:7" s="3" customFormat="1">
+    <row r="98" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="14"/>
@@ -2400,7 +2491,7 @@
       <c r="F98" s="2"/>
       <c r="G98" s="14"/>
     </row>
-    <row r="99" spans="1:7" s="3" customFormat="1">
+    <row r="99" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="14"/>
@@ -2409,7 +2500,7 @@
       <c r="F99" s="2"/>
       <c r="G99" s="14"/>
     </row>
-    <row r="100" spans="1:7" s="3" customFormat="1">
+    <row r="100" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="14"/>
@@ -2418,7 +2509,7 @@
       <c r="F100" s="2"/>
       <c r="G100" s="14"/>
     </row>
-    <row r="101" spans="1:7" s="3" customFormat="1">
+    <row r="101" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="14"/>
@@ -2427,7 +2518,7 @@
       <c r="F101" s="2"/>
       <c r="G101" s="14"/>
     </row>
-    <row r="102" spans="1:7" s="3" customFormat="1">
+    <row r="102" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="14"/>
@@ -2436,7 +2527,7 @@
       <c r="F102" s="2"/>
       <c r="G102" s="14"/>
     </row>
-    <row r="103" spans="1:7" s="3" customFormat="1">
+    <row r="103" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="14"/>
@@ -2445,7 +2536,7 @@
       <c r="F103" s="2"/>
       <c r="G103" s="14"/>
     </row>
-    <row r="104" spans="1:7" s="3" customFormat="1">
+    <row r="104" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="14"/>
@@ -2454,7 +2545,7 @@
       <c r="F104" s="2"/>
       <c r="G104" s="14"/>
     </row>
-    <row r="105" spans="1:7" s="3" customFormat="1">
+    <row r="105" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="14"/>
@@ -2463,7 +2554,7 @@
       <c r="F105" s="2"/>
       <c r="G105" s="14"/>
     </row>
-    <row r="106" spans="1:7" s="3" customFormat="1">
+    <row r="106" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="14"/>
@@ -2472,7 +2563,7 @@
       <c r="F106" s="2"/>
       <c r="G106" s="14"/>
     </row>
-    <row r="107" spans="1:7" s="3" customFormat="1">
+    <row r="107" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="14"/>
@@ -2481,7 +2572,7 @@
       <c r="F107" s="2"/>
       <c r="G107" s="14"/>
     </row>
-    <row r="108" spans="1:7" s="3" customFormat="1">
+    <row r="108" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="14"/>
@@ -2490,7 +2581,7 @@
       <c r="F108" s="2"/>
       <c r="G108" s="14"/>
     </row>
-    <row r="109" spans="1:7" s="3" customFormat="1">
+    <row r="109" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="14"/>
@@ -2499,7 +2590,7 @@
       <c r="F109" s="2"/>
       <c r="G109" s="14"/>
     </row>
-    <row r="110" spans="1:7" s="3" customFormat="1">
+    <row r="110" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="14"/>
@@ -2508,7 +2599,7 @@
       <c r="F110" s="2"/>
       <c r="G110" s="14"/>
     </row>
-    <row r="111" spans="1:7" s="3" customFormat="1">
+    <row r="111" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="14"/>
@@ -2517,7 +2608,7 @@
       <c r="F111" s="2"/>
       <c r="G111" s="14"/>
     </row>
-    <row r="112" spans="1:7" s="3" customFormat="1">
+    <row r="112" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="14"/>
@@ -2526,7 +2617,7 @@
       <c r="F112" s="2"/>
       <c r="G112" s="14"/>
     </row>
-    <row r="113" spans="1:7" s="3" customFormat="1">
+    <row r="113" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="14"/>
@@ -2535,7 +2626,7 @@
       <c r="F113" s="2"/>
       <c r="G113" s="14"/>
     </row>
-    <row r="114" spans="1:7" s="3" customFormat="1">
+    <row r="114" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="14"/>
@@ -2544,7 +2635,7 @@
       <c r="F114" s="2"/>
       <c r="G114" s="14"/>
     </row>
-    <row r="115" spans="1:7" s="3" customFormat="1">
+    <row r="115" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="14"/>
@@ -2553,7 +2644,7 @@
       <c r="F115" s="2"/>
       <c r="G115" s="14"/>
     </row>
-    <row r="116" spans="1:7" s="3" customFormat="1">
+    <row r="116" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="14"/>
@@ -2562,7 +2653,7 @@
       <c r="F116" s="2"/>
       <c r="G116" s="14"/>
     </row>
-    <row r="117" spans="1:7" s="3" customFormat="1">
+    <row r="117" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="14"/>
@@ -2571,7 +2662,7 @@
       <c r="F117" s="2"/>
       <c r="G117" s="14"/>
     </row>
-    <row r="118" spans="1:7" s="3" customFormat="1">
+    <row r="118" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="14"/>
@@ -2580,7 +2671,7 @@
       <c r="F118" s="2"/>
       <c r="G118" s="14"/>
     </row>
-    <row r="119" spans="1:7" s="3" customFormat="1">
+    <row r="119" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="14"/>
@@ -2589,7 +2680,7 @@
       <c r="F119" s="2"/>
       <c r="G119" s="14"/>
     </row>
-    <row r="120" spans="1:7" s="3" customFormat="1">
+    <row r="120" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="14"/>
@@ -2598,7 +2689,7 @@
       <c r="F120" s="2"/>
       <c r="G120" s="14"/>
     </row>
-    <row r="121" spans="1:7" s="3" customFormat="1">
+    <row r="121" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="14"/>
@@ -2607,7 +2698,7 @@
       <c r="F121" s="2"/>
       <c r="G121" s="14"/>
     </row>
-    <row r="122" spans="1:7" s="3" customFormat="1">
+    <row r="122" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="14"/>
@@ -2616,7 +2707,7 @@
       <c r="F122" s="2"/>
       <c r="G122" s="14"/>
     </row>
-    <row r="123" spans="1:7" s="3" customFormat="1">
+    <row r="123" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="14"/>
@@ -2625,7 +2716,7 @@
       <c r="F123" s="2"/>
       <c r="G123" s="14"/>
     </row>
-    <row r="124" spans="1:7" s="3" customFormat="1">
+    <row r="124" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="14"/>
@@ -2634,7 +2725,7 @@
       <c r="F124" s="2"/>
       <c r="G124" s="14"/>
     </row>
-    <row r="125" spans="1:7" s="3" customFormat="1">
+    <row r="125" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="14"/>
@@ -2643,7 +2734,7 @@
       <c r="F125" s="2"/>
       <c r="G125" s="14"/>
     </row>
-    <row r="126" spans="1:7" s="3" customFormat="1">
+    <row r="126" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="14"/>
@@ -2652,7 +2743,7 @@
       <c r="F126" s="2"/>
       <c r="G126" s="14"/>
     </row>
-    <row r="127" spans="1:7" s="3" customFormat="1">
+    <row r="127" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="14"/>
@@ -2661,7 +2752,7 @@
       <c r="F127" s="2"/>
       <c r="G127" s="14"/>
     </row>
-    <row r="128" spans="1:7" s="3" customFormat="1">
+    <row r="128" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="14"/>
@@ -2670,7 +2761,7 @@
       <c r="F128" s="2"/>
       <c r="G128" s="14"/>
     </row>
-    <row r="129" spans="1:7" s="3" customFormat="1">
+    <row r="129" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="14"/>
@@ -2679,7 +2770,7 @@
       <c r="F129" s="2"/>
       <c r="G129" s="14"/>
     </row>
-    <row r="130" spans="1:7" s="3" customFormat="1">
+    <row r="130" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="14"/>
@@ -2688,7 +2779,7 @@
       <c r="F130" s="2"/>
       <c r="G130" s="14"/>
     </row>
-    <row r="131" spans="1:7" s="3" customFormat="1">
+    <row r="131" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="14"/>
@@ -2697,7 +2788,7 @@
       <c r="F131" s="2"/>
       <c r="G131" s="14"/>
     </row>
-    <row r="132" spans="1:7" s="3" customFormat="1">
+    <row r="132" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="14"/>
@@ -2706,7 +2797,7 @@
       <c r="F132" s="2"/>
       <c r="G132" s="14"/>
     </row>
-    <row r="133" spans="1:7" s="3" customFormat="1">
+    <row r="133" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="14"/>
@@ -2715,7 +2806,7 @@
       <c r="F133" s="2"/>
       <c r="G133" s="14"/>
     </row>
-    <row r="134" spans="1:7" s="3" customFormat="1">
+    <row r="134" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="14"/>
@@ -2724,7 +2815,7 @@
       <c r="F134" s="2"/>
       <c r="G134" s="14"/>
     </row>
-    <row r="135" spans="1:7" s="3" customFormat="1">
+    <row r="135" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="14"/>
@@ -2733,7 +2824,7 @@
       <c r="F135" s="2"/>
       <c r="G135" s="14"/>
     </row>
-    <row r="136" spans="1:7" s="3" customFormat="1">
+    <row r="136" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="14"/>
@@ -2742,7 +2833,7 @@
       <c r="F136" s="2"/>
       <c r="G136" s="14"/>
     </row>
-    <row r="137" spans="1:7" s="3" customFormat="1">
+    <row r="137" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="14"/>
@@ -2751,7 +2842,7 @@
       <c r="F137" s="2"/>
       <c r="G137" s="14"/>
     </row>
-    <row r="138" spans="1:7" s="3" customFormat="1">
+    <row r="138" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="14"/>
@@ -2760,7 +2851,7 @@
       <c r="F138" s="2"/>
       <c r="G138" s="14"/>
     </row>
-    <row r="139" spans="1:7" s="3" customFormat="1">
+    <row r="139" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="14"/>
@@ -2769,7 +2860,7 @@
       <c r="F139" s="2"/>
       <c r="G139" s="14"/>
     </row>
-    <row r="140" spans="1:7" s="3" customFormat="1">
+    <row r="140" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="14"/>
@@ -2778,7 +2869,7 @@
       <c r="F140" s="2"/>
       <c r="G140" s="14"/>
     </row>
-    <row r="141" spans="1:7" s="3" customFormat="1">
+    <row r="141" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="14"/>
@@ -2787,7 +2878,7 @@
       <c r="F141" s="2"/>
       <c r="G141" s="14"/>
     </row>
-    <row r="142" spans="1:7" s="3" customFormat="1">
+    <row r="142" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="14"/>
@@ -2796,7 +2887,7 @@
       <c r="F142" s="2"/>
       <c r="G142" s="14"/>
     </row>
-    <row r="143" spans="1:7" s="3" customFormat="1">
+    <row r="143" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="14"/>
@@ -2805,7 +2896,7 @@
       <c r="F143" s="2"/>
       <c r="G143" s="14"/>
     </row>
-    <row r="144" spans="1:7" s="3" customFormat="1">
+    <row r="144" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="14"/>
@@ -2814,7 +2905,7 @@
       <c r="F144" s="2"/>
       <c r="G144" s="14"/>
     </row>
-    <row r="145" spans="1:7" s="3" customFormat="1">
+    <row r="145" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="14"/>
@@ -2823,7 +2914,7 @@
       <c r="F145" s="2"/>
       <c r="G145" s="14"/>
     </row>
-    <row r="146" spans="1:7" s="3" customFormat="1">
+    <row r="146" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="14"/>
@@ -2832,7 +2923,7 @@
       <c r="F146" s="2"/>
       <c r="G146" s="14"/>
     </row>
-    <row r="147" spans="1:7" s="3" customFormat="1">
+    <row r="147" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="14"/>
@@ -2841,7 +2932,7 @@
       <c r="F147" s="2"/>
       <c r="G147" s="14"/>
     </row>
-    <row r="148" spans="1:7" s="3" customFormat="1">
+    <row r="148" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="14"/>
@@ -2850,7 +2941,7 @@
       <c r="F148" s="2"/>
       <c r="G148" s="14"/>
     </row>
-    <row r="149" spans="1:7" s="3" customFormat="1">
+    <row r="149" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="14"/>
@@ -2859,7 +2950,7 @@
       <c r="F149" s="2"/>
       <c r="G149" s="14"/>
     </row>
-    <row r="150" spans="1:7" s="3" customFormat="1">
+    <row r="150" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="14"/>
@@ -2868,7 +2959,7 @@
       <c r="F150" s="2"/>
       <c r="G150" s="14"/>
     </row>
-    <row r="151" spans="1:7" s="3" customFormat="1">
+    <row r="151" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="14"/>
@@ -2877,7 +2968,7 @@
       <c r="F151" s="2"/>
       <c r="G151" s="14"/>
     </row>
-    <row r="152" spans="1:7" s="3" customFormat="1">
+    <row r="152" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="14"/>
@@ -2886,7 +2977,7 @@
       <c r="F152" s="2"/>
       <c r="G152" s="14"/>
     </row>
-    <row r="153" spans="1:7" s="3" customFormat="1">
+    <row r="153" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="14"/>
@@ -2895,7 +2986,7 @@
       <c r="F153" s="2"/>
       <c r="G153" s="14"/>
     </row>
-    <row r="154" spans="1:7" s="3" customFormat="1">
+    <row r="154" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="14"/>
@@ -2904,7 +2995,7 @@
       <c r="F154" s="2"/>
       <c r="G154" s="14"/>
     </row>
-    <row r="155" spans="1:7" s="3" customFormat="1">
+    <row r="155" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="14"/>
@@ -2913,7 +3004,7 @@
       <c r="F155" s="2"/>
       <c r="G155" s="14"/>
     </row>
-    <row r="156" spans="1:7" s="3" customFormat="1">
+    <row r="156" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="14"/>
@@ -2922,7 +3013,7 @@
       <c r="F156" s="2"/>
       <c r="G156" s="14"/>
     </row>
-    <row r="157" spans="1:7" s="3" customFormat="1">
+    <row r="157" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="14"/>
@@ -2931,7 +3022,7 @@
       <c r="F157" s="2"/>
       <c r="G157" s="14"/>
     </row>
-    <row r="158" spans="1:7" s="3" customFormat="1">
+    <row r="158" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="14"/>
@@ -2940,7 +3031,7 @@
       <c r="F158" s="2"/>
       <c r="G158" s="14"/>
     </row>
-    <row r="159" spans="1:7" s="3" customFormat="1">
+    <row r="159" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="14"/>
@@ -2949,7 +3040,7 @@
       <c r="F159" s="2"/>
       <c r="G159" s="14"/>
     </row>
-    <row r="160" spans="1:7" s="3" customFormat="1">
+    <row r="160" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="14"/>
@@ -2958,7 +3049,7 @@
       <c r="F160" s="2"/>
       <c r="G160" s="14"/>
     </row>
-    <row r="161" spans="1:7" s="3" customFormat="1">
+    <row r="161" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="14"/>
@@ -2967,7 +3058,7 @@
       <c r="F161" s="2"/>
       <c r="G161" s="14"/>
     </row>
-    <row r="162" spans="1:7" s="3" customFormat="1">
+    <row r="162" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="14"/>
@@ -2976,7 +3067,7 @@
       <c r="F162" s="2"/>
       <c r="G162" s="14"/>
     </row>
-    <row r="163" spans="1:7" s="3" customFormat="1">
+    <row r="163" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="14"/>
@@ -2985,7 +3076,7 @@
       <c r="F163" s="2"/>
       <c r="G163" s="14"/>
     </row>
-    <row r="164" spans="1:7" s="3" customFormat="1">
+    <row r="164" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="14"/>
@@ -2994,7 +3085,7 @@
       <c r="F164" s="2"/>
       <c r="G164" s="14"/>
     </row>
-    <row r="165" spans="1:7" s="3" customFormat="1">
+    <row r="165" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="14"/>
@@ -3003,7 +3094,7 @@
       <c r="F165" s="2"/>
       <c r="G165" s="14"/>
     </row>
-    <row r="166" spans="1:7" s="3" customFormat="1">
+    <row r="166" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="14"/>
@@ -3012,7 +3103,7 @@
       <c r="F166" s="2"/>
       <c r="G166" s="14"/>
     </row>
-    <row r="167" spans="1:7" s="3" customFormat="1">
+    <row r="167" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="14"/>
@@ -3021,7 +3112,7 @@
       <c r="F167" s="2"/>
       <c r="G167" s="14"/>
     </row>
-    <row r="168" spans="1:7" s="3" customFormat="1">
+    <row r="168" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="14"/>
@@ -3030,7 +3121,7 @@
       <c r="F168" s="2"/>
       <c r="G168" s="14"/>
     </row>
-    <row r="169" spans="1:7" s="3" customFormat="1">
+    <row r="169" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="14"/>
@@ -3039,7 +3130,7 @@
       <c r="F169" s="2"/>
       <c r="G169" s="14"/>
     </row>
-    <row r="170" spans="1:7" s="3" customFormat="1">
+    <row r="170" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="14"/>
@@ -3048,7 +3139,7 @@
       <c r="F170" s="2"/>
       <c r="G170" s="14"/>
     </row>
-    <row r="171" spans="1:7" s="3" customFormat="1">
+    <row r="171" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="14"/>
@@ -3057,7 +3148,7 @@
       <c r="F171" s="2"/>
       <c r="G171" s="14"/>
     </row>
-    <row r="172" spans="1:7" s="3" customFormat="1">
+    <row r="172" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="14"/>
@@ -3066,7 +3157,7 @@
       <c r="F172" s="2"/>
       <c r="G172" s="14"/>
     </row>
-    <row r="173" spans="1:7" s="3" customFormat="1">
+    <row r="173" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="14"/>
@@ -3075,7 +3166,7 @@
       <c r="F173" s="2"/>
       <c r="G173" s="14"/>
     </row>
-    <row r="174" spans="1:7" s="3" customFormat="1">
+    <row r="174" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="14"/>
@@ -3084,7 +3175,7 @@
       <c r="F174" s="2"/>
       <c r="G174" s="14"/>
     </row>
-    <row r="175" spans="1:7" s="3" customFormat="1">
+    <row r="175" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="14"/>
@@ -3093,7 +3184,7 @@
       <c r="F175" s="2"/>
       <c r="G175" s="14"/>
     </row>
-    <row r="176" spans="1:7" s="3" customFormat="1">
+    <row r="176" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="14"/>
@@ -3102,7 +3193,7 @@
       <c r="F176" s="2"/>
       <c r="G176" s="14"/>
     </row>
-    <row r="177" spans="1:7" s="3" customFormat="1">
+    <row r="177" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="14"/>
@@ -3111,7 +3202,7 @@
       <c r="F177" s="2"/>
       <c r="G177" s="14"/>
     </row>
-    <row r="178" spans="1:7" s="3" customFormat="1">
+    <row r="178" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="14"/>
@@ -3120,7 +3211,7 @@
       <c r="F178" s="2"/>
       <c r="G178" s="14"/>
     </row>
-    <row r="179" spans="1:7" s="3" customFormat="1">
+    <row r="179" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="14"/>
@@ -3129,7 +3220,7 @@
       <c r="F179" s="2"/>
       <c r="G179" s="14"/>
     </row>
-    <row r="180" spans="1:7" s="3" customFormat="1">
+    <row r="180" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="14"/>
@@ -3138,7 +3229,7 @@
       <c r="F180" s="2"/>
       <c r="G180" s="14"/>
     </row>
-    <row r="181" spans="1:7" s="3" customFormat="1">
+    <row r="181" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="14"/>
@@ -3147,7 +3238,7 @@
       <c r="F181" s="2"/>
       <c r="G181" s="14"/>
     </row>
-    <row r="182" spans="1:7" s="3" customFormat="1">
+    <row r="182" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="14"/>
@@ -3156,7 +3247,7 @@
       <c r="F182" s="2"/>
       <c r="G182" s="14"/>
     </row>
-    <row r="183" spans="1:7" s="3" customFormat="1">
+    <row r="183" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="14"/>
@@ -3165,7 +3256,7 @@
       <c r="F183" s="2"/>
       <c r="G183" s="14"/>
     </row>
-    <row r="184" spans="1:7" s="3" customFormat="1">
+    <row r="184" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="14"/>
@@ -3174,7 +3265,7 @@
       <c r="F184" s="2"/>
       <c r="G184" s="14"/>
     </row>
-    <row r="185" spans="1:7" s="3" customFormat="1">
+    <row r="185" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="14"/>
@@ -3183,7 +3274,7 @@
       <c r="F185" s="2"/>
       <c r="G185" s="14"/>
     </row>
-    <row r="186" spans="1:7" s="3" customFormat="1">
+    <row r="186" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="14"/>
@@ -3192,7 +3283,7 @@
       <c r="F186" s="2"/>
       <c r="G186" s="14"/>
     </row>
-    <row r="187" spans="1:7" s="3" customFormat="1">
+    <row r="187" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="14"/>
@@ -3201,7 +3292,7 @@
       <c r="F187" s="2"/>
       <c r="G187" s="14"/>
     </row>
-    <row r="188" spans="1:7" s="3" customFormat="1">
+    <row r="188" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="14"/>
@@ -3210,7 +3301,7 @@
       <c r="F188" s="2"/>
       <c r="G188" s="14"/>
     </row>
-    <row r="189" spans="1:7" s="3" customFormat="1">
+    <row r="189" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="14"/>
@@ -3219,7 +3310,7 @@
       <c r="F189" s="2"/>
       <c r="G189" s="14"/>
     </row>
-    <row r="190" spans="1:7" s="3" customFormat="1">
+    <row r="190" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="14"/>
@@ -3228,7 +3319,7 @@
       <c r="F190" s="2"/>
       <c r="G190" s="14"/>
     </row>
-    <row r="191" spans="1:7" s="3" customFormat="1">
+    <row r="191" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="14"/>
@@ -3237,7 +3328,7 @@
       <c r="F191" s="2"/>
       <c r="G191" s="14"/>
     </row>
-    <row r="192" spans="1:7" s="3" customFormat="1">
+    <row r="192" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="14"/>
@@ -3246,7 +3337,7 @@
       <c r="F192" s="2"/>
       <c r="G192" s="14"/>
     </row>
-    <row r="193" spans="1:7" s="3" customFormat="1">
+    <row r="193" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="14"/>
@@ -3255,7 +3346,7 @@
       <c r="F193" s="2"/>
       <c r="G193" s="14"/>
     </row>
-    <row r="194" spans="1:7" s="3" customFormat="1">
+    <row r="194" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="14"/>
@@ -3264,7 +3355,7 @@
       <c r="F194" s="2"/>
       <c r="G194" s="14"/>
     </row>
-    <row r="195" spans="1:7" s="3" customFormat="1">
+    <row r="195" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="14"/>
@@ -3273,7 +3364,7 @@
       <c r="F195" s="2"/>
       <c r="G195" s="14"/>
     </row>
-    <row r="196" spans="1:7" s="3" customFormat="1">
+    <row r="196" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="14"/>
@@ -3282,7 +3373,7 @@
       <c r="F196" s="2"/>
       <c r="G196" s="14"/>
     </row>
-    <row r="197" spans="1:7" s="3" customFormat="1">
+    <row r="197" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="14"/>
@@ -3291,7 +3382,7 @@
       <c r="F197" s="2"/>
       <c r="G197" s="14"/>
     </row>
-    <row r="198" spans="1:7" s="3" customFormat="1">
+    <row r="198" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="14"/>
@@ -3300,7 +3391,7 @@
       <c r="F198" s="2"/>
       <c r="G198" s="14"/>
     </row>
-    <row r="199" spans="1:7" s="3" customFormat="1">
+    <row r="199" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="14"/>
@@ -3309,7 +3400,7 @@
       <c r="F199" s="2"/>
       <c r="G199" s="14"/>
     </row>
-    <row r="200" spans="1:7" s="3" customFormat="1">
+    <row r="200" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="14"/>
@@ -3318,7 +3409,7 @@
       <c r="F200" s="2"/>
       <c r="G200" s="14"/>
     </row>
-    <row r="201" spans="1:7" s="3" customFormat="1">
+    <row r="201" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="14"/>
@@ -3327,7 +3418,7 @@
       <c r="F201" s="2"/>
       <c r="G201" s="14"/>
     </row>
-    <row r="202" spans="1:7" s="3" customFormat="1">
+    <row r="202" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="14"/>
@@ -3336,7 +3427,7 @@
       <c r="F202" s="2"/>
       <c r="G202" s="14"/>
     </row>
-    <row r="203" spans="1:7" s="3" customFormat="1">
+    <row r="203" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="14"/>
@@ -3345,7 +3436,7 @@
       <c r="F203" s="2"/>
       <c r="G203" s="14"/>
     </row>
-    <row r="204" spans="1:7" s="3" customFormat="1">
+    <row r="204" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="14"/>
@@ -3354,7 +3445,7 @@
       <c r="F204" s="2"/>
       <c r="G204" s="14"/>
     </row>
-    <row r="205" spans="1:7" s="3" customFormat="1">
+    <row r="205" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="14"/>
@@ -3363,7 +3454,7 @@
       <c r="F205" s="2"/>
       <c r="G205" s="14"/>
     </row>
-    <row r="206" spans="1:7" s="3" customFormat="1">
+    <row r="206" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="14"/>
@@ -3372,7 +3463,7 @@
       <c r="F206" s="2"/>
       <c r="G206" s="14"/>
     </row>
-    <row r="207" spans="1:7" s="3" customFormat="1">
+    <row r="207" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="14"/>
@@ -3381,7 +3472,7 @@
       <c r="F207" s="2"/>
       <c r="G207" s="14"/>
     </row>
-    <row r="208" spans="1:7" s="3" customFormat="1">
+    <row r="208" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="14"/>
@@ -3390,7 +3481,7 @@
       <c r="F208" s="2"/>
       <c r="G208" s="14"/>
     </row>
-    <row r="209" spans="1:7" s="3" customFormat="1">
+    <row r="209" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="14"/>
@@ -3399,7 +3490,7 @@
       <c r="F209" s="2"/>
       <c r="G209" s="14"/>
     </row>
-    <row r="210" spans="1:7" s="3" customFormat="1">
+    <row r="210" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="14"/>
@@ -3408,7 +3499,7 @@
       <c r="F210" s="2"/>
       <c r="G210" s="14"/>
     </row>
-    <row r="211" spans="1:7" s="3" customFormat="1">
+    <row r="211" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="14"/>
@@ -3417,7 +3508,7 @@
       <c r="F211" s="2"/>
       <c r="G211" s="14"/>
     </row>
-    <row r="212" spans="1:7" s="3" customFormat="1">
+    <row r="212" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="14"/>
@@ -3426,7 +3517,7 @@
       <c r="F212" s="2"/>
       <c r="G212" s="14"/>
     </row>
-    <row r="213" spans="1:7" s="3" customFormat="1">
+    <row r="213" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="14"/>
@@ -3435,7 +3526,7 @@
       <c r="F213" s="2"/>
       <c r="G213" s="14"/>
     </row>
-    <row r="214" spans="1:7" s="3" customFormat="1">
+    <row r="214" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="14"/>
@@ -3444,7 +3535,7 @@
       <c r="F214" s="2"/>
       <c r="G214" s="14"/>
     </row>
-    <row r="215" spans="1:7" s="3" customFormat="1">
+    <row r="215" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="14"/>
@@ -3453,7 +3544,7 @@
       <c r="F215" s="2"/>
       <c r="G215" s="14"/>
     </row>
-    <row r="216" spans="1:7" s="3" customFormat="1">
+    <row r="216" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="14"/>
@@ -3462,7 +3553,7 @@
       <c r="F216" s="2"/>
       <c r="G216" s="14"/>
     </row>
-    <row r="217" spans="1:7" s="3" customFormat="1">
+    <row r="217" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="14"/>
@@ -3471,7 +3562,7 @@
       <c r="F217" s="2"/>
       <c r="G217" s="14"/>
     </row>
-    <row r="218" spans="1:7" s="3" customFormat="1">
+    <row r="218" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="14"/>
@@ -3480,7 +3571,7 @@
       <c r="F218" s="2"/>
       <c r="G218" s="14"/>
     </row>
-    <row r="219" spans="1:7" s="3" customFormat="1">
+    <row r="219" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="14"/>
@@ -3489,7 +3580,7 @@
       <c r="F219" s="2"/>
       <c r="G219" s="14"/>
     </row>
-    <row r="220" spans="1:7" s="3" customFormat="1">
+    <row r="220" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="14"/>
@@ -3498,7 +3589,7 @@
       <c r="F220" s="2"/>
       <c r="G220" s="14"/>
     </row>
-    <row r="221" spans="1:7" s="3" customFormat="1">
+    <row r="221" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="14"/>
@@ -3507,7 +3598,7 @@
       <c r="F221" s="2"/>
       <c r="G221" s="14"/>
     </row>
-    <row r="222" spans="1:7" s="3" customFormat="1">
+    <row r="222" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="14"/>
@@ -3516,7 +3607,7 @@
       <c r="F222" s="2"/>
       <c r="G222" s="14"/>
     </row>
-    <row r="223" spans="1:7" s="3" customFormat="1">
+    <row r="223" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="14"/>
@@ -3525,7 +3616,7 @@
       <c r="F223" s="2"/>
       <c r="G223" s="14"/>
     </row>
-    <row r="224" spans="1:7" s="3" customFormat="1">
+    <row r="224" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="14"/>
@@ -3534,7 +3625,7 @@
       <c r="F224" s="2"/>
       <c r="G224" s="14"/>
     </row>
-    <row r="225" spans="1:7" s="3" customFormat="1">
+    <row r="225" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="14"/>
@@ -3543,7 +3634,7 @@
       <c r="F225" s="2"/>
       <c r="G225" s="14"/>
     </row>
-    <row r="226" spans="1:7" s="3" customFormat="1">
+    <row r="226" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="14"/>
@@ -3552,7 +3643,7 @@
       <c r="F226" s="2"/>
       <c r="G226" s="14"/>
     </row>
-    <row r="227" spans="1:7" s="3" customFormat="1">
+    <row r="227" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="14"/>
@@ -3561,7 +3652,7 @@
       <c r="F227" s="2"/>
       <c r="G227" s="14"/>
     </row>
-    <row r="228" spans="1:7" s="3" customFormat="1">
+    <row r="228" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="14"/>
@@ -3570,7 +3661,7 @@
       <c r="F228" s="2"/>
       <c r="G228" s="14"/>
     </row>
-    <row r="229" spans="1:7" s="3" customFormat="1">
+    <row r="229" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="14"/>
@@ -3579,7 +3670,7 @@
       <c r="F229" s="2"/>
       <c r="G229" s="14"/>
     </row>
-    <row r="230" spans="1:7" s="3" customFormat="1">
+    <row r="230" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="14"/>
@@ -3588,7 +3679,7 @@
       <c r="F230" s="2"/>
       <c r="G230" s="14"/>
     </row>
-    <row r="231" spans="1:7" s="3" customFormat="1">
+    <row r="231" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="14"/>
@@ -3597,7 +3688,7 @@
       <c r="F231" s="2"/>
       <c r="G231" s="14"/>
     </row>
-    <row r="232" spans="1:7" s="3" customFormat="1">
+    <row r="232" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="14"/>
@@ -3606,7 +3697,7 @@
       <c r="F232" s="2"/>
       <c r="G232" s="14"/>
     </row>
-    <row r="233" spans="1:7" s="3" customFormat="1">
+    <row r="233" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="14"/>
@@ -3615,7 +3706,7 @@
       <c r="F233" s="2"/>
       <c r="G233" s="14"/>
     </row>
-    <row r="234" spans="1:7" s="3" customFormat="1">
+    <row r="234" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="14"/>
@@ -3624,7 +3715,7 @@
       <c r="F234" s="2"/>
       <c r="G234" s="14"/>
     </row>
-    <row r="235" spans="1:7" s="3" customFormat="1">
+    <row r="235" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="14"/>
@@ -3633,7 +3724,7 @@
       <c r="F235" s="2"/>
       <c r="G235" s="14"/>
     </row>
-    <row r="236" spans="1:7" s="3" customFormat="1">
+    <row r="236" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="14"/>
@@ -3642,7 +3733,7 @@
       <c r="F236" s="2"/>
       <c r="G236" s="14"/>
     </row>
-    <row r="237" spans="1:7" s="3" customFormat="1">
+    <row r="237" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="14"/>
@@ -3651,7 +3742,7 @@
       <c r="F237" s="2"/>
       <c r="G237" s="14"/>
     </row>
-    <row r="238" spans="1:7" s="3" customFormat="1">
+    <row r="238" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="14"/>
@@ -3660,7 +3751,7 @@
       <c r="F238" s="2"/>
       <c r="G238" s="14"/>
     </row>
-    <row r="239" spans="1:7" s="3" customFormat="1">
+    <row r="239" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="14"/>
@@ -3669,7 +3760,7 @@
       <c r="F239" s="2"/>
       <c r="G239" s="14"/>
     </row>
-    <row r="240" spans="1:7" s="3" customFormat="1">
+    <row r="240" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="14"/>
@@ -3678,7 +3769,7 @@
       <c r="F240" s="2"/>
       <c r="G240" s="14"/>
     </row>
-    <row r="241" spans="1:7" s="3" customFormat="1">
+    <row r="241" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="14"/>
@@ -3687,7 +3778,7 @@
       <c r="F241" s="2"/>
       <c r="G241" s="14"/>
     </row>
-    <row r="242" spans="1:7" s="3" customFormat="1">
+    <row r="242" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="14"/>
@@ -3696,7 +3787,7 @@
       <c r="F242" s="2"/>
       <c r="G242" s="14"/>
     </row>
-    <row r="243" spans="1:7" s="3" customFormat="1">
+    <row r="243" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="14"/>
@@ -3705,7 +3796,7 @@
       <c r="F243" s="2"/>
       <c r="G243" s="14"/>
     </row>
-    <row r="244" spans="1:7" s="3" customFormat="1">
+    <row r="244" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="14"/>
@@ -3714,7 +3805,7 @@
       <c r="F244" s="2"/>
       <c r="G244" s="14"/>
     </row>
-    <row r="245" spans="1:7" s="3" customFormat="1">
+    <row r="245" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="14"/>
@@ -3723,7 +3814,7 @@
       <c r="F245" s="2"/>
       <c r="G245" s="14"/>
     </row>
-    <row r="246" spans="1:7" s="3" customFormat="1">
+    <row r="246" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="14"/>
@@ -3732,7 +3823,7 @@
       <c r="F246" s="2"/>
       <c r="G246" s="14"/>
     </row>
-    <row r="247" spans="1:7" s="3" customFormat="1">
+    <row r="247" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="14"/>
@@ -3741,7 +3832,7 @@
       <c r="F247" s="2"/>
       <c r="G247" s="14"/>
     </row>
-    <row r="248" spans="1:7" s="3" customFormat="1">
+    <row r="248" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="14"/>
@@ -3750,7 +3841,7 @@
       <c r="F248" s="2"/>
       <c r="G248" s="14"/>
     </row>
-    <row r="249" spans="1:7" s="3" customFormat="1">
+    <row r="249" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="14"/>
@@ -3759,7 +3850,7 @@
       <c r="F249" s="2"/>
       <c r="G249" s="14"/>
     </row>
-    <row r="250" spans="1:7" s="3" customFormat="1">
+    <row r="250" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="14"/>
@@ -3768,7 +3859,7 @@
       <c r="F250" s="2"/>
       <c r="G250" s="14"/>
     </row>
-    <row r="251" spans="1:7" s="3" customFormat="1">
+    <row r="251" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="14"/>
@@ -3777,7 +3868,7 @@
       <c r="F251" s="2"/>
       <c r="G251" s="14"/>
     </row>
-    <row r="252" spans="1:7" s="3" customFormat="1">
+    <row r="252" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="14"/>
@@ -3786,7 +3877,7 @@
       <c r="F252" s="2"/>
       <c r="G252" s="14"/>
     </row>
-    <row r="253" spans="1:7" s="3" customFormat="1">
+    <row r="253" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="14"/>
@@ -3795,7 +3886,7 @@
       <c r="F253" s="2"/>
       <c r="G253" s="14"/>
     </row>
-    <row r="254" spans="1:7" s="3" customFormat="1">
+    <row r="254" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="14"/>
@@ -3804,7 +3895,7 @@
       <c r="F254" s="2"/>
       <c r="G254" s="14"/>
     </row>
-    <row r="255" spans="1:7" s="3" customFormat="1">
+    <row r="255" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="14"/>
@@ -3813,7 +3904,7 @@
       <c r="F255" s="2"/>
       <c r="G255" s="14"/>
     </row>
-    <row r="256" spans="1:7" s="3" customFormat="1">
+    <row r="256" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="14"/>
@@ -3822,7 +3913,7 @@
       <c r="F256" s="2"/>
       <c r="G256" s="14"/>
     </row>
-    <row r="257" spans="1:7" s="3" customFormat="1">
+    <row r="257" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="14"/>
@@ -3831,7 +3922,7 @@
       <c r="F257" s="2"/>
       <c r="G257" s="14"/>
     </row>
-    <row r="258" spans="1:7" s="3" customFormat="1">
+    <row r="258" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="14"/>
@@ -3840,7 +3931,7 @@
       <c r="F258" s="2"/>
       <c r="G258" s="14"/>
     </row>
-    <row r="259" spans="1:7" s="3" customFormat="1">
+    <row r="259" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="14"/>
@@ -3849,7 +3940,7 @@
       <c r="F259" s="2"/>
       <c r="G259" s="14"/>
     </row>
-    <row r="260" spans="1:7" s="3" customFormat="1">
+    <row r="260" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="14"/>
@@ -3858,7 +3949,7 @@
       <c r="F260" s="2"/>
       <c r="G260" s="14"/>
     </row>
-    <row r="261" spans="1:7" s="3" customFormat="1">
+    <row r="261" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="14"/>
@@ -3867,7 +3958,7 @@
       <c r="F261" s="2"/>
       <c r="G261" s="14"/>
     </row>
-    <row r="262" spans="1:7" s="3" customFormat="1">
+    <row r="262" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="14"/>
@@ -3876,7 +3967,7 @@
       <c r="F262" s="2"/>
       <c r="G262" s="14"/>
     </row>
-    <row r="263" spans="1:7" s="3" customFormat="1">
+    <row r="263" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="14"/>
@@ -3885,7 +3976,7 @@
       <c r="F263" s="2"/>
       <c r="G263" s="14"/>
     </row>
-    <row r="264" spans="1:7" s="3" customFormat="1">
+    <row r="264" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="14"/>
@@ -3894,7 +3985,7 @@
       <c r="F264" s="2"/>
       <c r="G264" s="14"/>
     </row>
-    <row r="265" spans="1:7" s="3" customFormat="1">
+    <row r="265" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="14"/>
@@ -3903,7 +3994,7 @@
       <c r="F265" s="2"/>
       <c r="G265" s="14"/>
     </row>
-    <row r="266" spans="1:7" s="3" customFormat="1">
+    <row r="266" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="14"/>
@@ -3912,7 +4003,7 @@
       <c r="F266" s="2"/>
       <c r="G266" s="14"/>
     </row>
-    <row r="267" spans="1:7" s="3" customFormat="1">
+    <row r="267" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="14"/>
@@ -3921,7 +4012,7 @@
       <c r="F267" s="2"/>
       <c r="G267" s="14"/>
     </row>
-    <row r="268" spans="1:7" s="3" customFormat="1">
+    <row r="268" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="14"/>
@@ -3930,7 +4021,7 @@
       <c r="F268" s="2"/>
       <c r="G268" s="14"/>
     </row>
-    <row r="269" spans="1:7" s="3" customFormat="1">
+    <row r="269" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="14"/>
@@ -3939,7 +4030,7 @@
       <c r="F269" s="2"/>
       <c r="G269" s="14"/>
     </row>
-    <row r="270" spans="1:7" s="3" customFormat="1">
+    <row r="270" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="14"/>
@@ -3948,7 +4039,7 @@
       <c r="F270" s="2"/>
       <c r="G270" s="14"/>
     </row>
-    <row r="271" spans="1:7" s="3" customFormat="1">
+    <row r="271" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="14"/>
@@ -3957,7 +4048,7 @@
       <c r="F271" s="2"/>
       <c r="G271" s="14"/>
     </row>
-    <row r="272" spans="1:7" s="3" customFormat="1">
+    <row r="272" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="14"/>
@@ -3966,7 +4057,7 @@
       <c r="F272" s="2"/>
       <c r="G272" s="14"/>
     </row>
-    <row r="273" spans="1:7" s="3" customFormat="1">
+    <row r="273" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="14"/>
@@ -3975,7 +4066,7 @@
       <c r="F273" s="2"/>
       <c r="G273" s="14"/>
     </row>
-    <row r="274" spans="1:7" s="3" customFormat="1">
+    <row r="274" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="14"/>
@@ -3984,7 +4075,7 @@
       <c r="F274" s="2"/>
       <c r="G274" s="14"/>
     </row>
-    <row r="275" spans="1:7" s="3" customFormat="1">
+    <row r="275" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="14"/>
@@ -3993,7 +4084,7 @@
       <c r="F275" s="2"/>
       <c r="G275" s="14"/>
     </row>
-    <row r="276" spans="1:7" s="3" customFormat="1">
+    <row r="276" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="14"/>
@@ -4002,7 +4093,7 @@
       <c r="F276" s="2"/>
       <c r="G276" s="14"/>
     </row>
-    <row r="277" spans="1:7" s="3" customFormat="1">
+    <row r="277" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="14"/>
@@ -4011,7 +4102,7 @@
       <c r="F277" s="2"/>
       <c r="G277" s="14"/>
     </row>
-    <row r="278" spans="1:7" s="3" customFormat="1">
+    <row r="278" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="14"/>
@@ -4020,7 +4111,7 @@
       <c r="F278" s="2"/>
       <c r="G278" s="14"/>
     </row>
-    <row r="279" spans="1:7" s="3" customFormat="1">
+    <row r="279" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="14"/>
@@ -4029,7 +4120,7 @@
       <c r="F279" s="2"/>
       <c r="G279" s="14"/>
     </row>
-    <row r="280" spans="1:7" s="3" customFormat="1">
+    <row r="280" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="14"/>
@@ -4038,7 +4129,7 @@
       <c r="F280" s="2"/>
       <c r="G280" s="14"/>
     </row>
-    <row r="281" spans="1:7" s="3" customFormat="1">
+    <row r="281" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="14"/>
@@ -4047,7 +4138,7 @@
       <c r="F281" s="2"/>
       <c r="G281" s="14"/>
     </row>
-    <row r="282" spans="1:7" s="3" customFormat="1">
+    <row r="282" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="14"/>
@@ -4056,7 +4147,7 @@
       <c r="F282" s="2"/>
       <c r="G282" s="14"/>
     </row>
-    <row r="283" spans="1:7" s="3" customFormat="1">
+    <row r="283" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="14"/>
@@ -4065,7 +4156,7 @@
       <c r="F283" s="2"/>
       <c r="G283" s="14"/>
     </row>
-    <row r="284" spans="1:7" s="3" customFormat="1">
+    <row r="284" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="14"/>
@@ -4074,7 +4165,7 @@
       <c r="F284" s="2"/>
       <c r="G284" s="14"/>
     </row>
-    <row r="285" spans="1:7" s="3" customFormat="1">
+    <row r="285" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="14"/>
@@ -4083,7 +4174,7 @@
       <c r="F285" s="2"/>
       <c r="G285" s="14"/>
     </row>
-    <row r="286" spans="1:7" s="3" customFormat="1">
+    <row r="286" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="14"/>
@@ -4092,7 +4183,7 @@
       <c r="F286" s="2"/>
       <c r="G286" s="14"/>
     </row>
-    <row r="287" spans="1:7" s="3" customFormat="1">
+    <row r="287" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="14"/>
@@ -4101,7 +4192,7 @@
       <c r="F287" s="2"/>
       <c r="G287" s="14"/>
     </row>
-    <row r="288" spans="1:7" s="3" customFormat="1">
+    <row r="288" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="14"/>
@@ -4110,7 +4201,7 @@
       <c r="F288" s="2"/>
       <c r="G288" s="14"/>
     </row>
-    <row r="289" spans="1:7" s="3" customFormat="1">
+    <row r="289" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="14"/>
@@ -4119,7 +4210,7 @@
       <c r="F289" s="2"/>
       <c r="G289" s="14"/>
     </row>
-    <row r="290" spans="1:7" s="3" customFormat="1">
+    <row r="290" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="14"/>
@@ -4128,7 +4219,7 @@
       <c r="F290" s="2"/>
       <c r="G290" s="14"/>
     </row>
-    <row r="291" spans="1:7" s="3" customFormat="1">
+    <row r="291" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="14"/>
@@ -4137,7 +4228,7 @@
       <c r="F291" s="2"/>
       <c r="G291" s="14"/>
     </row>
-    <row r="292" spans="1:7" s="3" customFormat="1">
+    <row r="292" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="14"/>
@@ -4146,7 +4237,7 @@
       <c r="F292" s="2"/>
       <c r="G292" s="14"/>
     </row>
-    <row r="293" spans="1:7" s="3" customFormat="1">
+    <row r="293" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="14"/>
@@ -4155,7 +4246,7 @@
       <c r="F293" s="2"/>
       <c r="G293" s="14"/>
     </row>
-    <row r="294" spans="1:7" s="3" customFormat="1">
+    <row r="294" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="14"/>
@@ -4164,7 +4255,7 @@
       <c r="F294" s="2"/>
       <c r="G294" s="14"/>
     </row>
-    <row r="295" spans="1:7" s="3" customFormat="1">
+    <row r="295" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="14"/>
@@ -4173,7 +4264,7 @@
       <c r="F295" s="2"/>
       <c r="G295" s="14"/>
     </row>
-    <row r="296" spans="1:7" s="3" customFormat="1">
+    <row r="296" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="14"/>
@@ -4182,7 +4273,7 @@
       <c r="F296" s="2"/>
       <c r="G296" s="14"/>
     </row>
-    <row r="297" spans="1:7" s="3" customFormat="1">
+    <row r="297" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="14"/>
@@ -4191,7 +4282,7 @@
       <c r="F297" s="2"/>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" spans="1:7" s="3" customFormat="1">
+    <row r="298" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="14"/>
@@ -4200,7 +4291,7 @@
       <c r="F298" s="2"/>
       <c r="G298" s="14"/>
     </row>
-    <row r="299" spans="1:7" s="3" customFormat="1">
+    <row r="299" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="14"/>
@@ -4209,7 +4300,7 @@
       <c r="F299" s="2"/>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" spans="1:7" s="3" customFormat="1">
+    <row r="300" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="14"/>
@@ -4218,7 +4309,7 @@
       <c r="F300" s="2"/>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="1:7" s="3" customFormat="1">
+    <row r="301" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="14"/>
@@ -4227,7 +4318,7 @@
       <c r="F301" s="2"/>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="1:7" s="3" customFormat="1">
+    <row r="302" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="14"/>
@@ -4236,7 +4327,7 @@
       <c r="F302" s="2"/>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="1:7" s="3" customFormat="1">
+    <row r="303" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="14"/>
@@ -4245,7 +4336,7 @@
       <c r="F303" s="2"/>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="1:7" s="3" customFormat="1">
+    <row r="304" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="14"/>
@@ -4254,7 +4345,7 @@
       <c r="F304" s="2"/>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="1:7" s="3" customFormat="1">
+    <row r="305" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="14"/>
@@ -4263,7 +4354,7 @@
       <c r="F305" s="2"/>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" spans="1:7" s="3" customFormat="1">
+    <row r="306" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="14"/>
@@ -4272,7 +4363,7 @@
       <c r="F306" s="2"/>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="1:7" s="3" customFormat="1">
+    <row r="307" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="14"/>
@@ -4281,7 +4372,7 @@
       <c r="F307" s="2"/>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" spans="1:7" s="3" customFormat="1">
+    <row r="308" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="14"/>
@@ -4290,7 +4381,7 @@
       <c r="F308" s="2"/>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" spans="1:7" s="3" customFormat="1">
+    <row r="309" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="14"/>
@@ -4299,7 +4390,7 @@
       <c r="F309" s="2"/>
       <c r="G309" s="14"/>
     </row>
-    <row r="310" spans="1:7" s="3" customFormat="1">
+    <row r="310" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="14"/>
@@ -4308,7 +4399,7 @@
       <c r="F310" s="2"/>
       <c r="G310" s="14"/>
     </row>
-    <row r="311" spans="1:7" s="3" customFormat="1">
+    <row r="311" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="14"/>
@@ -4317,7 +4408,7 @@
       <c r="F311" s="2"/>
       <c r="G311" s="14"/>
     </row>
-    <row r="312" spans="1:7" s="3" customFormat="1">
+    <row r="312" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="14"/>
@@ -4326,7 +4417,7 @@
       <c r="F312" s="2"/>
       <c r="G312" s="14"/>
     </row>
-    <row r="313" spans="1:7" s="3" customFormat="1">
+    <row r="313" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="14"/>
@@ -4335,7 +4426,7 @@
       <c r="F313" s="2"/>
       <c r="G313" s="14"/>
     </row>
-    <row r="314" spans="1:7" s="3" customFormat="1">
+    <row r="314" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="14"/>
@@ -4344,7 +4435,7 @@
       <c r="F314" s="2"/>
       <c r="G314" s="14"/>
     </row>
-    <row r="315" spans="1:7" s="3" customFormat="1">
+    <row r="315" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="14"/>
@@ -4353,7 +4444,7 @@
       <c r="F315" s="2"/>
       <c r="G315" s="14"/>
     </row>
-    <row r="316" spans="1:7" s="3" customFormat="1">
+    <row r="316" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="14"/>
@@ -4362,7 +4453,7 @@
       <c r="F316" s="2"/>
       <c r="G316" s="14"/>
     </row>
-    <row r="317" spans="1:7" s="3" customFormat="1">
+    <row r="317" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="14"/>
@@ -4371,7 +4462,7 @@
       <c r="F317" s="2"/>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" spans="1:7" s="3" customFormat="1">
+    <row r="318" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="14"/>
@@ -4380,7 +4471,7 @@
       <c r="F318" s="2"/>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" spans="1:7" s="3" customFormat="1">
+    <row r="319" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="14"/>
@@ -4389,7 +4480,7 @@
       <c r="F319" s="2"/>
       <c r="G319" s="14"/>
     </row>
-    <row r="320" spans="1:7" s="3" customFormat="1">
+    <row r="320" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="14"/>
@@ -4398,7 +4489,7 @@
       <c r="F320" s="2"/>
       <c r="G320" s="14"/>
     </row>
-    <row r="321" spans="1:7" s="3" customFormat="1">
+    <row r="321" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="14"/>
@@ -4407,7 +4498,7 @@
       <c r="F321" s="2"/>
       <c r="G321" s="14"/>
     </row>
-    <row r="322" spans="1:7" s="3" customFormat="1">
+    <row r="322" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="14"/>
@@ -4416,7 +4507,7 @@
       <c r="F322" s="2"/>
       <c r="G322" s="14"/>
     </row>
-    <row r="323" spans="1:7" s="3" customFormat="1">
+    <row r="323" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="14"/>
@@ -4425,7 +4516,7 @@
       <c r="F323" s="2"/>
       <c r="G323" s="14"/>
     </row>
-    <row r="324" spans="1:7" s="3" customFormat="1">
+    <row r="324" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="14"/>
@@ -4434,7 +4525,7 @@
       <c r="F324" s="2"/>
       <c r="G324" s="14"/>
     </row>
-    <row r="325" spans="1:7" s="3" customFormat="1">
+    <row r="325" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="14"/>
@@ -4443,7 +4534,7 @@
       <c r="F325" s="2"/>
       <c r="G325" s="14"/>
     </row>
-    <row r="326" spans="1:7" s="3" customFormat="1">
+    <row r="326" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="14"/>
@@ -4452,7 +4543,7 @@
       <c r="F326" s="2"/>
       <c r="G326" s="14"/>
     </row>
-    <row r="327" spans="1:7" s="3" customFormat="1">
+    <row r="327" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="14"/>
@@ -4461,7 +4552,7 @@
       <c r="F327" s="2"/>
       <c r="G327" s="14"/>
     </row>
-    <row r="328" spans="1:7" s="3" customFormat="1">
+    <row r="328" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="14"/>
@@ -4470,7 +4561,7 @@
       <c r="F328" s="2"/>
       <c r="G328" s="14"/>
     </row>
-    <row r="329" spans="1:7" s="3" customFormat="1">
+    <row r="329" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="14"/>
@@ -4479,7 +4570,7 @@
       <c r="F329" s="2"/>
       <c r="G329" s="14"/>
     </row>
-    <row r="330" spans="1:7" s="3" customFormat="1">
+    <row r="330" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="14"/>
@@ -4488,7 +4579,7 @@
       <c r="F330" s="2"/>
       <c r="G330" s="14"/>
     </row>
-    <row r="331" spans="1:7" s="3" customFormat="1">
+    <row r="331" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="14"/>
@@ -4497,7 +4588,7 @@
       <c r="F331" s="2"/>
       <c r="G331" s="14"/>
     </row>
-    <row r="332" spans="1:7" s="3" customFormat="1">
+    <row r="332" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="14"/>
@@ -4506,7 +4597,7 @@
       <c r="F332" s="2"/>
       <c r="G332" s="14"/>
     </row>
-    <row r="333" spans="1:7" s="3" customFormat="1">
+    <row r="333" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="14"/>
@@ -4515,7 +4606,7 @@
       <c r="F333" s="2"/>
       <c r="G333" s="14"/>
     </row>
-    <row r="334" spans="1:7" s="3" customFormat="1">
+    <row r="334" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="14"/>
@@ -4524,7 +4615,7 @@
       <c r="F334" s="2"/>
       <c r="G334" s="14"/>
     </row>
-    <row r="335" spans="1:7" s="3" customFormat="1">
+    <row r="335" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="14"/>
@@ -4533,7 +4624,7 @@
       <c r="F335" s="2"/>
       <c r="G335" s="14"/>
     </row>
-    <row r="336" spans="1:7" s="3" customFormat="1">
+    <row r="336" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="14"/>
@@ -4542,7 +4633,7 @@
       <c r="F336" s="2"/>
       <c r="G336" s="14"/>
     </row>
-    <row r="337" spans="1:7" s="3" customFormat="1">
+    <row r="337" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="14"/>
@@ -4551,7 +4642,7 @@
       <c r="F337" s="2"/>
       <c r="G337" s="14"/>
     </row>
-    <row r="338" spans="1:7" s="3" customFormat="1">
+    <row r="338" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="14"/>
@@ -4560,7 +4651,7 @@
       <c r="F338" s="2"/>
       <c r="G338" s="14"/>
     </row>
-    <row r="339" spans="1:7" s="3" customFormat="1">
+    <row r="339" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="14"/>
@@ -4569,7 +4660,7 @@
       <c r="F339" s="2"/>
       <c r="G339" s="14"/>
     </row>
-    <row r="340" spans="1:7" s="3" customFormat="1">
+    <row r="340" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="14"/>
@@ -4578,7 +4669,7 @@
       <c r="F340" s="2"/>
       <c r="G340" s="14"/>
     </row>
-    <row r="341" spans="1:7" s="3" customFormat="1">
+    <row r="341" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="14"/>
@@ -4587,7 +4678,7 @@
       <c r="F341" s="2"/>
       <c r="G341" s="14"/>
     </row>
-    <row r="342" spans="1:7" s="3" customFormat="1">
+    <row r="342" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="14"/>
@@ -4596,7 +4687,7 @@
       <c r="F342" s="2"/>
       <c r="G342" s="14"/>
     </row>
-    <row r="343" spans="1:7" s="3" customFormat="1">
+    <row r="343" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="14"/>
@@ -4605,7 +4696,7 @@
       <c r="F343" s="2"/>
       <c r="G343" s="14"/>
     </row>
-    <row r="344" spans="1:7" s="3" customFormat="1">
+    <row r="344" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="14"/>
@@ -4614,7 +4705,7 @@
       <c r="F344" s="2"/>
       <c r="G344" s="14"/>
     </row>
-    <row r="345" spans="1:7" s="3" customFormat="1">
+    <row r="345" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="14"/>
@@ -4623,7 +4714,7 @@
       <c r="F345" s="2"/>
       <c r="G345" s="14"/>
     </row>
-    <row r="346" spans="1:7" s="3" customFormat="1">
+    <row r="346" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="14"/>
@@ -4632,7 +4723,7 @@
       <c r="F346" s="2"/>
       <c r="G346" s="14"/>
     </row>
-    <row r="347" spans="1:7" s="3" customFormat="1">
+    <row r="347" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="14"/>
@@ -4641,7 +4732,7 @@
       <c r="F347" s="2"/>
       <c r="G347" s="14"/>
     </row>
-    <row r="348" spans="1:7" s="3" customFormat="1">
+    <row r="348" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="14"/>
@@ -4650,7 +4741,7 @@
       <c r="F348" s="2"/>
       <c r="G348" s="14"/>
     </row>
-    <row r="349" spans="1:7" s="3" customFormat="1">
+    <row r="349" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="14"/>
@@ -4659,7 +4750,7 @@
       <c r="F349" s="2"/>
       <c r="G349" s="14"/>
     </row>
-    <row r="350" spans="1:7" s="3" customFormat="1">
+    <row r="350" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="14"/>
@@ -4668,7 +4759,7 @@
       <c r="F350" s="2"/>
       <c r="G350" s="14"/>
     </row>
-    <row r="351" spans="1:7" s="3" customFormat="1">
+    <row r="351" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="14"/>
@@ -4677,7 +4768,7 @@
       <c r="F351" s="2"/>
       <c r="G351" s="14"/>
     </row>
-    <row r="352" spans="1:7" s="3" customFormat="1">
+    <row r="352" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="14"/>
@@ -4686,7 +4777,7 @@
       <c r="F352" s="2"/>
       <c r="G352" s="14"/>
     </row>
-    <row r="353" spans="1:7" s="3" customFormat="1">
+    <row r="353" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="14"/>
@@ -4695,7 +4786,7 @@
       <c r="F353" s="2"/>
       <c r="G353" s="14"/>
     </row>
-    <row r="354" spans="1:7" s="3" customFormat="1">
+    <row r="354" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="14"/>
@@ -4704,7 +4795,7 @@
       <c r="F354" s="2"/>
       <c r="G354" s="14"/>
     </row>
-    <row r="355" spans="1:7" s="3" customFormat="1">
+    <row r="355" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="14"/>
@@ -4713,7 +4804,7 @@
       <c r="F355" s="2"/>
       <c r="G355" s="14"/>
     </row>
-    <row r="356" spans="1:7" s="3" customFormat="1">
+    <row r="356" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="14"/>
@@ -4722,7 +4813,7 @@
       <c r="F356" s="2"/>
       <c r="G356" s="14"/>
     </row>
-    <row r="357" spans="1:7" s="3" customFormat="1">
+    <row r="357" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="14"/>
@@ -4731,7 +4822,7 @@
       <c r="F357" s="2"/>
       <c r="G357" s="14"/>
     </row>
-    <row r="358" spans="1:7" s="3" customFormat="1">
+    <row r="358" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="14"/>
@@ -4740,7 +4831,7 @@
       <c r="F358" s="2"/>
       <c r="G358" s="14"/>
     </row>
-    <row r="359" spans="1:7" s="3" customFormat="1">
+    <row r="359" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="14"/>
@@ -4749,7 +4840,7 @@
       <c r="F359" s="2"/>
       <c r="G359" s="14"/>
     </row>
-    <row r="360" spans="1:7" s="3" customFormat="1">
+    <row r="360" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="14"/>
@@ -4758,7 +4849,7 @@
       <c r="F360" s="2"/>
       <c r="G360" s="14"/>
     </row>
-    <row r="361" spans="1:7" s="3" customFormat="1">
+    <row r="361" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="14"/>
@@ -4767,7 +4858,7 @@
       <c r="F361" s="2"/>
       <c r="G361" s="14"/>
     </row>
-    <row r="362" spans="1:7" s="3" customFormat="1">
+    <row r="362" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="14"/>
@@ -4776,7 +4867,7 @@
       <c r="F362" s="2"/>
       <c r="G362" s="14"/>
     </row>
-    <row r="363" spans="1:7" s="3" customFormat="1">
+    <row r="363" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="14"/>
@@ -4785,7 +4876,7 @@
       <c r="F363" s="2"/>
       <c r="G363" s="14"/>
     </row>
-    <row r="364" spans="1:7" s="3" customFormat="1">
+    <row r="364" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="14"/>
@@ -4794,7 +4885,7 @@
       <c r="F364" s="2"/>
       <c r="G364" s="14"/>
     </row>
-    <row r="365" spans="1:7" s="3" customFormat="1">
+    <row r="365" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="14"/>
@@ -4803,7 +4894,7 @@
       <c r="F365" s="2"/>
       <c r="G365" s="14"/>
     </row>
-    <row r="366" spans="1:7" s="3" customFormat="1">
+    <row r="366" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="14"/>
@@ -4812,7 +4903,7 @@
       <c r="F366" s="2"/>
       <c r="G366" s="14"/>
     </row>
-    <row r="367" spans="1:7" s="3" customFormat="1">
+    <row r="367" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="14"/>
@@ -4821,7 +4912,7 @@
       <c r="F367" s="2"/>
       <c r="G367" s="14"/>
     </row>
-    <row r="368" spans="1:7" s="3" customFormat="1">
+    <row r="368" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="14"/>
@@ -4830,7 +4921,7 @@
       <c r="F368" s="2"/>
       <c r="G368" s="14"/>
     </row>
-    <row r="369" spans="1:7" s="3" customFormat="1">
+    <row r="369" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="14"/>
@@ -4839,7 +4930,7 @@
       <c r="F369" s="2"/>
       <c r="G369" s="14"/>
     </row>
-    <row r="370" spans="1:7" s="3" customFormat="1">
+    <row r="370" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="14"/>
@@ -4848,7 +4939,7 @@
       <c r="F370" s="2"/>
       <c r="G370" s="14"/>
     </row>
-    <row r="371" spans="1:7" s="3" customFormat="1">
+    <row r="371" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="14"/>
@@ -4857,7 +4948,7 @@
       <c r="F371" s="2"/>
       <c r="G371" s="14"/>
     </row>
-    <row r="372" spans="1:7" s="3" customFormat="1">
+    <row r="372" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="14"/>
@@ -4866,7 +4957,7 @@
       <c r="F372" s="2"/>
       <c r="G372" s="14"/>
     </row>
-    <row r="373" spans="1:7" s="3" customFormat="1">
+    <row r="373" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="14"/>
@@ -4875,7 +4966,7 @@
       <c r="F373" s="2"/>
       <c r="G373" s="14"/>
     </row>
-    <row r="374" spans="1:7" s="3" customFormat="1">
+    <row r="374" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="14"/>
@@ -4884,7 +4975,7 @@
       <c r="F374" s="2"/>
       <c r="G374" s="14"/>
     </row>
-    <row r="375" spans="1:7" s="3" customFormat="1">
+    <row r="375" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="14"/>
@@ -4893,7 +4984,7 @@
       <c r="F375" s="2"/>
       <c r="G375" s="14"/>
     </row>
-    <row r="376" spans="1:7" s="3" customFormat="1">
+    <row r="376" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="14"/>
@@ -4902,7 +4993,7 @@
       <c r="F376" s="2"/>
       <c r="G376" s="14"/>
     </row>
-    <row r="377" spans="1:7" s="3" customFormat="1">
+    <row r="377" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="14"/>
@@ -4911,7 +5002,7 @@
       <c r="F377" s="2"/>
       <c r="G377" s="14"/>
     </row>
-    <row r="378" spans="1:7" s="3" customFormat="1">
+    <row r="378" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="14"/>
@@ -4920,7 +5011,7 @@
       <c r="F378" s="2"/>
       <c r="G378" s="14"/>
     </row>
-    <row r="379" spans="1:7" s="3" customFormat="1">
+    <row r="379" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="14"/>
@@ -4929,7 +5020,7 @@
       <c r="F379" s="2"/>
       <c r="G379" s="14"/>
     </row>
-    <row r="380" spans="1:7" s="3" customFormat="1">
+    <row r="380" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="14"/>
@@ -4938,7 +5029,7 @@
       <c r="F380" s="2"/>
       <c r="G380" s="14"/>
     </row>
-    <row r="381" spans="1:7" s="3" customFormat="1">
+    <row r="381" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="14"/>
@@ -4947,7 +5038,7 @@
       <c r="F381" s="2"/>
       <c r="G381" s="14"/>
     </row>
-    <row r="382" spans="1:7" s="3" customFormat="1">
+    <row r="382" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="14"/>
@@ -4956,7 +5047,7 @@
       <c r="F382" s="2"/>
       <c r="G382" s="14"/>
     </row>
-    <row r="383" spans="1:7" s="3" customFormat="1">
+    <row r="383" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="14"/>
@@ -4965,7 +5056,7 @@
       <c r="F383" s="2"/>
       <c r="G383" s="14"/>
     </row>
-    <row r="384" spans="1:7" s="3" customFormat="1">
+    <row r="384" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="14"/>
@@ -4974,7 +5065,7 @@
       <c r="F384" s="2"/>
       <c r="G384" s="14"/>
     </row>
-    <row r="385" spans="1:7" s="3" customFormat="1">
+    <row r="385" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="14"/>
@@ -4983,7 +5074,7 @@
       <c r="F385" s="2"/>
       <c r="G385" s="14"/>
     </row>
-    <row r="386" spans="1:7" s="3" customFormat="1">
+    <row r="386" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="14"/>
@@ -4992,7 +5083,7 @@
       <c r="F386" s="2"/>
       <c r="G386" s="14"/>
     </row>
-    <row r="387" spans="1:7" s="3" customFormat="1">
+    <row r="387" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="14"/>
@@ -5001,7 +5092,7 @@
       <c r="F387" s="2"/>
       <c r="G387" s="14"/>
     </row>
-    <row r="388" spans="1:7" s="3" customFormat="1">
+    <row r="388" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="14"/>
@@ -5010,7 +5101,7 @@
       <c r="F388" s="2"/>
       <c r="G388" s="14"/>
     </row>
-    <row r="389" spans="1:7" s="3" customFormat="1">
+    <row r="389" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="14"/>
@@ -5019,7 +5110,7 @@
       <c r="F389" s="2"/>
       <c r="G389" s="14"/>
     </row>
-    <row r="390" spans="1:7" s="3" customFormat="1">
+    <row r="390" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="14"/>
@@ -5028,7 +5119,7 @@
       <c r="F390" s="2"/>
       <c r="G390" s="14"/>
     </row>
-    <row r="391" spans="1:7" s="3" customFormat="1">
+    <row r="391" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="14"/>
@@ -5037,7 +5128,7 @@
       <c r="F391" s="2"/>
       <c r="G391" s="14"/>
     </row>
-    <row r="392" spans="1:7" s="3" customFormat="1">
+    <row r="392" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="14"/>
@@ -5046,7 +5137,7 @@
       <c r="F392" s="2"/>
       <c r="G392" s="14"/>
     </row>
-    <row r="393" spans="1:7" s="3" customFormat="1">
+    <row r="393" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="14"/>
@@ -5055,7 +5146,7 @@
       <c r="F393" s="2"/>
       <c r="G393" s="14"/>
     </row>
-    <row r="394" spans="1:7" s="3" customFormat="1">
+    <row r="394" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="14"/>
@@ -5064,7 +5155,7 @@
       <c r="F394" s="2"/>
       <c r="G394" s="14"/>
     </row>
-    <row r="395" spans="1:7" s="3" customFormat="1">
+    <row r="395" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="14"/>
@@ -5073,7 +5164,7 @@
       <c r="F395" s="2"/>
       <c r="G395" s="14"/>
     </row>
-    <row r="396" spans="1:7" s="3" customFormat="1">
+    <row r="396" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="14"/>
@@ -5082,7 +5173,7 @@
       <c r="F396" s="2"/>
       <c r="G396" s="14"/>
     </row>
-    <row r="397" spans="1:7" s="3" customFormat="1">
+    <row r="397" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="14"/>
@@ -5091,7 +5182,7 @@
       <c r="F397" s="2"/>
       <c r="G397" s="14"/>
     </row>
-    <row r="398" spans="1:7" s="3" customFormat="1">
+    <row r="398" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="14"/>
@@ -5100,7 +5191,7 @@
       <c r="F398" s="2"/>
       <c r="G398" s="14"/>
     </row>
-    <row r="399" spans="1:7" s="3" customFormat="1">
+    <row r="399" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="14"/>
@@ -5109,7 +5200,7 @@
       <c r="F399" s="2"/>
       <c r="G399" s="14"/>
     </row>
-    <row r="400" spans="1:7" s="3" customFormat="1">
+    <row r="400" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="14"/>
@@ -5118,7 +5209,7 @@
       <c r="F400" s="2"/>
       <c r="G400" s="14"/>
     </row>
-    <row r="401" spans="1:7" s="3" customFormat="1">
+    <row r="401" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="14"/>
@@ -5127,7 +5218,7 @@
       <c r="F401" s="2"/>
       <c r="G401" s="14"/>
     </row>
-    <row r="402" spans="1:7" s="3" customFormat="1">
+    <row r="402" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="14"/>
@@ -5136,7 +5227,7 @@
       <c r="F402" s="2"/>
       <c r="G402" s="14"/>
     </row>
-    <row r="403" spans="1:7" s="3" customFormat="1">
+    <row r="403" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="14"/>
@@ -5145,7 +5236,7 @@
       <c r="F403" s="2"/>
       <c r="G403" s="14"/>
     </row>
-    <row r="404" spans="1:7" s="3" customFormat="1">
+    <row r="404" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="14"/>
@@ -5154,7 +5245,7 @@
       <c r="F404" s="2"/>
       <c r="G404" s="14"/>
     </row>
-    <row r="405" spans="1:7" s="3" customFormat="1">
+    <row r="405" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="14"/>
@@ -5163,7 +5254,7 @@
       <c r="F405" s="2"/>
       <c r="G405" s="14"/>
     </row>
-    <row r="406" spans="1:7" s="3" customFormat="1">
+    <row r="406" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="14"/>
@@ -5172,7 +5263,7 @@
       <c r="F406" s="2"/>
       <c r="G406" s="14"/>
     </row>
-    <row r="407" spans="1:7" s="3" customFormat="1">
+    <row r="407" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="14"/>
@@ -5181,7 +5272,7 @@
       <c r="F407" s="2"/>
       <c r="G407" s="14"/>
     </row>
-    <row r="408" spans="1:7" s="3" customFormat="1">
+    <row r="408" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="14"/>
@@ -5190,7 +5281,7 @@
       <c r="F408" s="2"/>
       <c r="G408" s="14"/>
     </row>
-    <row r="409" spans="1:7" s="3" customFormat="1">
+    <row r="409" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="14"/>
@@ -5199,7 +5290,7 @@
       <c r="F409" s="2"/>
       <c r="G409" s="14"/>
     </row>
-    <row r="410" spans="1:7" s="3" customFormat="1">
+    <row r="410" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="14"/>
@@ -5208,7 +5299,7 @@
       <c r="F410" s="2"/>
       <c r="G410" s="14"/>
     </row>
-    <row r="411" spans="1:7" s="3" customFormat="1">
+    <row r="411" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="14"/>
@@ -5217,7 +5308,7 @@
       <c r="F411" s="2"/>
       <c r="G411" s="14"/>
     </row>
-    <row r="412" spans="1:7" s="3" customFormat="1">
+    <row r="412" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="14"/>
@@ -5226,7 +5317,7 @@
       <c r="F412" s="2"/>
       <c r="G412" s="14"/>
     </row>
-    <row r="413" spans="1:7" s="3" customFormat="1">
+    <row r="413" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="14"/>
@@ -5235,7 +5326,7 @@
       <c r="F413" s="2"/>
       <c r="G413" s="14"/>
     </row>
-    <row r="414" spans="1:7" s="3" customFormat="1">
+    <row r="414" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="14"/>
@@ -5244,7 +5335,7 @@
       <c r="F414" s="2"/>
       <c r="G414" s="14"/>
     </row>
-    <row r="415" spans="1:7" s="3" customFormat="1">
+    <row r="415" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="14"/>
@@ -5253,7 +5344,7 @@
       <c r="F415" s="2"/>
       <c r="G415" s="14"/>
     </row>
-    <row r="416" spans="1:7" s="3" customFormat="1">
+    <row r="416" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="14"/>
@@ -5262,7 +5353,7 @@
       <c r="F416" s="2"/>
       <c r="G416" s="14"/>
     </row>
-    <row r="417" spans="1:7" s="3" customFormat="1">
+    <row r="417" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="14"/>
@@ -5271,7 +5362,7 @@
       <c r="F417" s="2"/>
       <c r="G417" s="14"/>
     </row>
-    <row r="418" spans="1:7" s="3" customFormat="1">
+    <row r="418" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="14"/>
@@ -5280,7 +5371,7 @@
       <c r="F418" s="2"/>
       <c r="G418" s="14"/>
     </row>
-    <row r="419" spans="1:7" s="3" customFormat="1">
+    <row r="419" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="14"/>
@@ -5289,7 +5380,7 @@
       <c r="F419" s="2"/>
       <c r="G419" s="14"/>
     </row>
-    <row r="420" spans="1:7" s="3" customFormat="1">
+    <row r="420" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="14"/>
@@ -5298,7 +5389,7 @@
       <c r="F420" s="2"/>
       <c r="G420" s="14"/>
     </row>
-    <row r="421" spans="1:7" s="3" customFormat="1">
+    <row r="421" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="14"/>
@@ -5307,7 +5398,7 @@
       <c r="F421" s="2"/>
       <c r="G421" s="14"/>
     </row>
-    <row r="422" spans="1:7" s="3" customFormat="1">
+    <row r="422" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="14"/>
@@ -5316,7 +5407,7 @@
       <c r="F422" s="2"/>
       <c r="G422" s="14"/>
     </row>
-    <row r="423" spans="1:7" s="3" customFormat="1">
+    <row r="423" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="14"/>
@@ -5325,7 +5416,7 @@
       <c r="F423" s="2"/>
       <c r="G423" s="14"/>
     </row>
-    <row r="424" spans="1:7" s="3" customFormat="1">
+    <row r="424" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="14"/>
@@ -5334,7 +5425,7 @@
       <c r="F424" s="2"/>
       <c r="G424" s="14"/>
     </row>
-    <row r="425" spans="1:7" s="3" customFormat="1">
+    <row r="425" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="14"/>
@@ -5343,7 +5434,7 @@
       <c r="F425" s="2"/>
       <c r="G425" s="14"/>
     </row>
-    <row r="426" spans="1:7" s="3" customFormat="1">
+    <row r="426" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="14"/>
@@ -5352,7 +5443,7 @@
       <c r="F426" s="2"/>
       <c r="G426" s="14"/>
     </row>
-    <row r="427" spans="1:7" s="3" customFormat="1">
+    <row r="427" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="14"/>
@@ -5361,7 +5452,7 @@
       <c r="F427" s="2"/>
       <c r="G427" s="14"/>
     </row>
-    <row r="428" spans="1:7" s="3" customFormat="1">
+    <row r="428" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="14"/>
@@ -5370,7 +5461,7 @@
       <c r="F428" s="2"/>
       <c r="G428" s="14"/>
     </row>
-    <row r="429" spans="1:7" s="3" customFormat="1">
+    <row r="429" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="14"/>
@@ -5379,7 +5470,7 @@
       <c r="F429" s="2"/>
       <c r="G429" s="14"/>
     </row>
-    <row r="430" spans="1:7" s="3" customFormat="1">
+    <row r="430" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="14"/>
@@ -5388,7 +5479,7 @@
       <c r="F430" s="2"/>
       <c r="G430" s="14"/>
     </row>
-    <row r="431" spans="1:7" s="3" customFormat="1">
+    <row r="431" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="14"/>
@@ -5397,7 +5488,7 @@
       <c r="F431" s="2"/>
       <c r="G431" s="14"/>
     </row>
-    <row r="432" spans="1:7" s="3" customFormat="1">
+    <row r="432" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="14"/>
@@ -5406,7 +5497,7 @@
       <c r="F432" s="2"/>
       <c r="G432" s="14"/>
     </row>
-    <row r="433" spans="1:7" s="3" customFormat="1">
+    <row r="433" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="14"/>
@@ -5415,7 +5506,7 @@
       <c r="F433" s="2"/>
       <c r="G433" s="14"/>
     </row>
-    <row r="434" spans="1:7" s="3" customFormat="1">
+    <row r="434" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="14"/>
@@ -5424,7 +5515,7 @@
       <c r="F434" s="2"/>
       <c r="G434" s="14"/>
     </row>
-    <row r="435" spans="1:7" s="3" customFormat="1">
+    <row r="435" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="14"/>
@@ -5433,7 +5524,7 @@
       <c r="F435" s="2"/>
       <c r="G435" s="14"/>
     </row>
-    <row r="436" spans="1:7" s="3" customFormat="1">
+    <row r="436" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="14"/>
@@ -5442,7 +5533,7 @@
       <c r="F436" s="2"/>
       <c r="G436" s="14"/>
     </row>
-    <row r="437" spans="1:7" s="3" customFormat="1">
+    <row r="437" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="14"/>
@@ -5451,7 +5542,7 @@
       <c r="F437" s="2"/>
       <c r="G437" s="14"/>
     </row>
-    <row r="438" spans="1:7" s="3" customFormat="1">
+    <row r="438" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="14"/>
@@ -5460,7 +5551,7 @@
       <c r="F438" s="2"/>
       <c r="G438" s="14"/>
     </row>
-    <row r="439" spans="1:7" s="3" customFormat="1">
+    <row r="439" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="14"/>
@@ -5469,7 +5560,7 @@
       <c r="F439" s="2"/>
       <c r="G439" s="14"/>
     </row>
-    <row r="440" spans="1:7" s="3" customFormat="1">
+    <row r="440" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="14"/>
@@ -5478,7 +5569,7 @@
       <c r="F440" s="2"/>
       <c r="G440" s="14"/>
     </row>
-    <row r="441" spans="1:7" s="3" customFormat="1">
+    <row r="441" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="14"/>
@@ -5487,7 +5578,7 @@
       <c r="F441" s="2"/>
       <c r="G441" s="14"/>
     </row>
-    <row r="442" spans="1:7" s="3" customFormat="1">
+    <row r="442" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="14"/>
@@ -5496,7 +5587,7 @@
       <c r="F442" s="2"/>
       <c r="G442" s="14"/>
     </row>
-    <row r="443" spans="1:7" s="3" customFormat="1">
+    <row r="443" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="14"/>
@@ -5505,7 +5596,7 @@
       <c r="F443" s="2"/>
       <c r="G443" s="14"/>
     </row>
-    <row r="444" spans="1:7" s="3" customFormat="1">
+    <row r="444" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="14"/>
@@ -5514,7 +5605,7 @@
       <c r="F444" s="2"/>
       <c r="G444" s="14"/>
     </row>
-    <row r="445" spans="1:7" s="3" customFormat="1">
+    <row r="445" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="14"/>
@@ -5523,7 +5614,7 @@
       <c r="F445" s="2"/>
       <c r="G445" s="14"/>
     </row>
-    <row r="446" spans="1:7" s="3" customFormat="1">
+    <row r="446" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="14"/>
@@ -5532,7 +5623,7 @@
       <c r="F446" s="2"/>
       <c r="G446" s="14"/>
     </row>
-    <row r="447" spans="1:7" s="3" customFormat="1">
+    <row r="447" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="14"/>
@@ -5541,7 +5632,7 @@
       <c r="F447" s="2"/>
       <c r="G447" s="14"/>
     </row>
-    <row r="448" spans="1:7" s="3" customFormat="1">
+    <row r="448" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="14"/>
@@ -5550,7 +5641,7 @@
       <c r="F448" s="2"/>
       <c r="G448" s="14"/>
     </row>
-    <row r="449" spans="1:7" s="3" customFormat="1">
+    <row r="449" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="14"/>
@@ -5559,7 +5650,7 @@
       <c r="F449" s="2"/>
       <c r="G449" s="14"/>
     </row>
-    <row r="450" spans="1:7" s="3" customFormat="1">
+    <row r="450" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="14"/>
@@ -5568,7 +5659,7 @@
       <c r="F450" s="2"/>
       <c r="G450" s="14"/>
     </row>
-    <row r="451" spans="1:7" s="3" customFormat="1">
+    <row r="451" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="14"/>
@@ -5577,7 +5668,7 @@
       <c r="F451" s="2"/>
       <c r="G451" s="14"/>
     </row>
-    <row r="452" spans="1:7" s="3" customFormat="1">
+    <row r="452" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="14"/>
@@ -5586,7 +5677,7 @@
       <c r="F452" s="2"/>
       <c r="G452" s="14"/>
     </row>
-    <row r="453" spans="1:7" s="3" customFormat="1">
+    <row r="453" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="14"/>
@@ -5595,7 +5686,7 @@
       <c r="F453" s="2"/>
       <c r="G453" s="14"/>
     </row>
-    <row r="454" spans="1:7" s="3" customFormat="1">
+    <row r="454" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="14"/>
@@ -5604,7 +5695,7 @@
       <c r="F454" s="2"/>
       <c r="G454" s="14"/>
     </row>
-    <row r="455" spans="1:7" s="3" customFormat="1">
+    <row r="455" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="14"/>
@@ -5613,7 +5704,7 @@
       <c r="F455" s="2"/>
       <c r="G455" s="14"/>
     </row>
-    <row r="456" spans="1:7" s="3" customFormat="1">
+    <row r="456" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="14"/>
@@ -5622,7 +5713,7 @@
       <c r="F456" s="2"/>
       <c r="G456" s="14"/>
     </row>
-    <row r="457" spans="1:7" s="3" customFormat="1">
+    <row r="457" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="14"/>
@@ -5631,7 +5722,7 @@
       <c r="F457" s="2"/>
       <c r="G457" s="14"/>
     </row>
-    <row r="458" spans="1:7" s="3" customFormat="1">
+    <row r="458" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="14"/>
@@ -5640,7 +5731,7 @@
       <c r="F458" s="2"/>
       <c r="G458" s="14"/>
     </row>
-    <row r="459" spans="1:7" s="3" customFormat="1">
+    <row r="459" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="14"/>
@@ -5649,7 +5740,7 @@
       <c r="F459" s="2"/>
       <c r="G459" s="14"/>
     </row>
-    <row r="460" spans="1:7" s="3" customFormat="1">
+    <row r="460" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="14"/>
@@ -5658,7 +5749,7 @@
       <c r="F460" s="2"/>
       <c r="G460" s="14"/>
     </row>
-    <row r="461" spans="1:7" s="3" customFormat="1">
+    <row r="461" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="14"/>
@@ -5667,7 +5758,7 @@
       <c r="F461" s="2"/>
       <c r="G461" s="14"/>
     </row>
-    <row r="462" spans="1:7" s="3" customFormat="1">
+    <row r="462" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="14"/>
@@ -5676,7 +5767,7 @@
       <c r="F462" s="2"/>
       <c r="G462" s="14"/>
     </row>
-    <row r="463" spans="1:7" s="3" customFormat="1">
+    <row r="463" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="14"/>
@@ -5685,7 +5776,7 @@
       <c r="F463" s="2"/>
       <c r="G463" s="14"/>
     </row>
-    <row r="464" spans="1:7" s="3" customFormat="1">
+    <row r="464" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="14"/>
@@ -5694,7 +5785,7 @@
       <c r="F464" s="2"/>
       <c r="G464" s="14"/>
     </row>
-    <row r="465" spans="1:7" s="3" customFormat="1">
+    <row r="465" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="14"/>
@@ -5703,7 +5794,7 @@
       <c r="F465" s="2"/>
       <c r="G465" s="14"/>
     </row>
-    <row r="466" spans="1:7" s="3" customFormat="1">
+    <row r="466" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="14"/>
@@ -5712,7 +5803,7 @@
       <c r="F466" s="2"/>
       <c r="G466" s="14"/>
     </row>
-    <row r="467" spans="1:7" s="3" customFormat="1">
+    <row r="467" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="14"/>
@@ -5721,7 +5812,7 @@
       <c r="F467" s="2"/>
       <c r="G467" s="14"/>
     </row>
-    <row r="468" spans="1:7" s="3" customFormat="1">
+    <row r="468" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="14"/>
@@ -5730,7 +5821,7 @@
       <c r="F468" s="2"/>
       <c r="G468" s="14"/>
     </row>
-    <row r="469" spans="1:7" s="3" customFormat="1">
+    <row r="469" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="14"/>
@@ -5739,7 +5830,7 @@
       <c r="F469" s="2"/>
       <c r="G469" s="14"/>
     </row>
-    <row r="470" spans="1:7" s="3" customFormat="1">
+    <row r="470" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="14"/>
@@ -5748,7 +5839,7 @@
       <c r="F470" s="2"/>
       <c r="G470" s="14"/>
     </row>
-    <row r="471" spans="1:7" s="3" customFormat="1">
+    <row r="471" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="14"/>
@@ -5757,7 +5848,7 @@
       <c r="F471" s="2"/>
       <c r="G471" s="14"/>
     </row>
-    <row r="472" spans="1:7" s="3" customFormat="1">
+    <row r="472" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="14"/>
@@ -5766,7 +5857,7 @@
       <c r="F472" s="2"/>
       <c r="G472" s="14"/>
     </row>
-    <row r="473" spans="1:7" s="3" customFormat="1">
+    <row r="473" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="14"/>
@@ -5775,7 +5866,7 @@
       <c r="F473" s="2"/>
       <c r="G473" s="14"/>
     </row>
-    <row r="474" spans="1:7" s="3" customFormat="1">
+    <row r="474" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="14"/>
@@ -5784,7 +5875,7 @@
       <c r="F474" s="2"/>
       <c r="G474" s="14"/>
     </row>
-    <row r="475" spans="1:7" s="3" customFormat="1">
+    <row r="475" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="14"/>
@@ -5793,7 +5884,7 @@
       <c r="F475" s="2"/>
       <c r="G475" s="14"/>
     </row>
-    <row r="476" spans="1:7" s="3" customFormat="1">
+    <row r="476" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="14"/>
@@ -5802,7 +5893,7 @@
       <c r="F476" s="2"/>
       <c r="G476" s="14"/>
     </row>
-    <row r="477" spans="1:7" s="3" customFormat="1">
+    <row r="477" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="14"/>
@@ -5811,7 +5902,7 @@
       <c r="F477" s="2"/>
       <c r="G477" s="14"/>
     </row>
-    <row r="478" spans="1:7" s="3" customFormat="1">
+    <row r="478" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="14"/>
@@ -5820,7 +5911,7 @@
       <c r="F478" s="2"/>
       <c r="G478" s="14"/>
     </row>
-    <row r="479" spans="1:7" s="3" customFormat="1">
+    <row r="479" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="14"/>
@@ -5829,7 +5920,7 @@
       <c r="F479" s="2"/>
       <c r="G479" s="14"/>
     </row>
-    <row r="480" spans="1:7" s="3" customFormat="1">
+    <row r="480" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="14"/>
@@ -5838,7 +5929,7 @@
       <c r="F480" s="2"/>
       <c r="G480" s="14"/>
     </row>
-    <row r="481" spans="1:7" s="3" customFormat="1">
+    <row r="481" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="14"/>
@@ -5847,7 +5938,7 @@
       <c r="F481" s="2"/>
       <c r="G481" s="14"/>
     </row>
-    <row r="482" spans="1:7" s="3" customFormat="1">
+    <row r="482" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="14"/>
@@ -5856,7 +5947,7 @@
       <c r="F482" s="2"/>
       <c r="G482" s="14"/>
     </row>
-    <row r="483" spans="1:7" s="3" customFormat="1">
+    <row r="483" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="14"/>
@@ -5865,7 +5956,7 @@
       <c r="F483" s="2"/>
       <c r="G483" s="14"/>
     </row>
-    <row r="484" spans="1:7" s="3" customFormat="1">
+    <row r="484" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="14"/>
@@ -5874,7 +5965,7 @@
       <c r="F484" s="2"/>
       <c r="G484" s="14"/>
     </row>
-    <row r="485" spans="1:7" s="3" customFormat="1">
+    <row r="485" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="14"/>
@@ -5883,7 +5974,7 @@
       <c r="F485" s="2"/>
       <c r="G485" s="14"/>
     </row>
-    <row r="486" spans="1:7" s="3" customFormat="1">
+    <row r="486" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="14"/>
@@ -5892,7 +5983,7 @@
       <c r="F486" s="2"/>
       <c r="G486" s="14"/>
     </row>
-    <row r="487" spans="1:7" s="3" customFormat="1">
+    <row r="487" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="14"/>
@@ -5901,7 +5992,7 @@
       <c r="F487" s="2"/>
       <c r="G487" s="14"/>
     </row>
-    <row r="488" spans="1:7" s="3" customFormat="1">
+    <row r="488" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="14"/>
@@ -5910,7 +6001,7 @@
       <c r="F488" s="2"/>
       <c r="G488" s="14"/>
     </row>
-    <row r="489" spans="1:7" s="3" customFormat="1">
+    <row r="489" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="14"/>
@@ -5919,7 +6010,7 @@
       <c r="F489" s="2"/>
       <c r="G489" s="14"/>
     </row>
-    <row r="490" spans="1:7" s="3" customFormat="1">
+    <row r="490" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="14"/>
@@ -5928,7 +6019,7 @@
       <c r="F490" s="2"/>
       <c r="G490" s="14"/>
     </row>
-    <row r="491" spans="1:7" s="3" customFormat="1">
+    <row r="491" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="14"/>
@@ -5937,7 +6028,7 @@
       <c r="F491" s="2"/>
       <c r="G491" s="14"/>
     </row>
-    <row r="492" spans="1:7" s="3" customFormat="1">
+    <row r="492" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="14"/>
@@ -5946,7 +6037,7 @@
       <c r="F492" s="2"/>
       <c r="G492" s="14"/>
     </row>
-    <row r="493" spans="1:7" s="3" customFormat="1">
+    <row r="493" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="14"/>
@@ -5955,7 +6046,7 @@
       <c r="F493" s="2"/>
       <c r="G493" s="14"/>
     </row>
-    <row r="494" spans="1:7" s="3" customFormat="1">
+    <row r="494" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="14"/>
@@ -5964,7 +6055,7 @@
       <c r="F494" s="2"/>
       <c r="G494" s="14"/>
     </row>
-    <row r="495" spans="1:7" s="3" customFormat="1">
+    <row r="495" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="14"/>
@@ -5973,7 +6064,7 @@
       <c r="F495" s="2"/>
       <c r="G495" s="14"/>
     </row>
-    <row r="496" spans="1:7" s="3" customFormat="1">
+    <row r="496" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="14"/>
@@ -5982,7 +6073,7 @@
       <c r="F496" s="2"/>
       <c r="G496" s="14"/>
     </row>
-    <row r="497" spans="1:7" s="3" customFormat="1">
+    <row r="497" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="14"/>
@@ -5991,7 +6082,7 @@
       <c r="F497" s="2"/>
       <c r="G497" s="14"/>
     </row>
-    <row r="498" spans="1:7" s="3" customFormat="1">
+    <row r="498" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="14"/>
@@ -6000,7 +6091,7 @@
       <c r="F498" s="2"/>
       <c r="G498" s="14"/>
     </row>
-    <row r="499" spans="1:7" s="3" customFormat="1">
+    <row r="499" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="14"/>
@@ -6009,7 +6100,7 @@
       <c r="F499" s="2"/>
       <c r="G499" s="14"/>
     </row>
-    <row r="500" spans="1:7" s="3" customFormat="1">
+    <row r="500" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="14"/>
@@ -6018,7 +6109,7 @@
       <c r="F500" s="2"/>
       <c r="G500" s="14"/>
     </row>
-    <row r="501" spans="1:7" s="3" customFormat="1">
+    <row r="501" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="14"/>
@@ -6027,7 +6118,7 @@
       <c r="F501" s="2"/>
       <c r="G501" s="14"/>
     </row>
-    <row r="502" spans="1:7" s="3" customFormat="1">
+    <row r="502" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="14"/>
@@ -6036,7 +6127,7 @@
       <c r="F502" s="2"/>
       <c r="G502" s="14"/>
     </row>
-    <row r="503" spans="1:7" s="3" customFormat="1">
+    <row r="503" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="14"/>
@@ -6045,7 +6136,7 @@
       <c r="F503" s="2"/>
       <c r="G503" s="14"/>
     </row>
-    <row r="504" spans="1:7" s="3" customFormat="1">
+    <row r="504" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="14"/>
@@ -6054,7 +6145,7 @@
       <c r="F504" s="2"/>
       <c r="G504" s="14"/>
     </row>
-    <row r="505" spans="1:7" s="3" customFormat="1">
+    <row r="505" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="14"/>
@@ -6063,7 +6154,7 @@
       <c r="F505" s="2"/>
       <c r="G505" s="14"/>
     </row>
-    <row r="506" spans="1:7" s="3" customFormat="1">
+    <row r="506" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="14"/>
@@ -6072,7 +6163,7 @@
       <c r="F506" s="2"/>
       <c r="G506" s="14"/>
     </row>
-    <row r="507" spans="1:7" s="3" customFormat="1">
+    <row r="507" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="14"/>
@@ -6081,7 +6172,7 @@
       <c r="F507" s="2"/>
       <c r="G507" s="14"/>
     </row>
-    <row r="508" spans="1:7" s="3" customFormat="1">
+    <row r="508" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="14"/>
@@ -6090,7 +6181,7 @@
       <c r="F508" s="2"/>
       <c r="G508" s="14"/>
     </row>
-    <row r="509" spans="1:7" s="3" customFormat="1">
+    <row r="509" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="14"/>
@@ -6099,7 +6190,7 @@
       <c r="F509" s="2"/>
       <c r="G509" s="14"/>
     </row>
-    <row r="510" spans="1:7" s="3" customFormat="1">
+    <row r="510" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="14"/>
@@ -6108,7 +6199,7 @@
       <c r="F510" s="2"/>
       <c r="G510" s="14"/>
     </row>
-    <row r="511" spans="1:7" s="3" customFormat="1">
+    <row r="511" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="14"/>
@@ -6117,7 +6208,7 @@
       <c r="F511" s="2"/>
       <c r="G511" s="14"/>
     </row>
-    <row r="512" spans="1:7" s="3" customFormat="1">
+    <row r="512" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="14"/>
@@ -6126,7 +6217,7 @@
       <c r="F512" s="2"/>
       <c r="G512" s="14"/>
     </row>
-    <row r="513" spans="1:7" s="3" customFormat="1">
+    <row r="513" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="14"/>
@@ -6135,7 +6226,7 @@
       <c r="F513" s="2"/>
       <c r="G513" s="14"/>
     </row>
-    <row r="514" spans="1:7" s="3" customFormat="1">
+    <row r="514" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="14"/>
@@ -6144,7 +6235,7 @@
       <c r="F514" s="2"/>
       <c r="G514" s="14"/>
     </row>
-    <row r="515" spans="1:7" s="3" customFormat="1">
+    <row r="515" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="14"/>
@@ -6153,7 +6244,7 @@
       <c r="F515" s="2"/>
       <c r="G515" s="14"/>
     </row>
-    <row r="516" spans="1:7" s="3" customFormat="1">
+    <row r="516" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="14"/>
@@ -6162,7 +6253,7 @@
       <c r="F516" s="2"/>
       <c r="G516" s="14"/>
     </row>
-    <row r="517" spans="1:7" s="3" customFormat="1">
+    <row r="517" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="14"/>
@@ -6171,7 +6262,7 @@
       <c r="F517" s="2"/>
       <c r="G517" s="14"/>
     </row>
-    <row r="518" spans="1:7" s="3" customFormat="1">
+    <row r="518" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="14"/>
@@ -6180,7 +6271,7 @@
       <c r="F518" s="2"/>
       <c r="G518" s="14"/>
     </row>
-    <row r="519" spans="1:7" s="3" customFormat="1">
+    <row r="519" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="14"/>
@@ -6189,7 +6280,7 @@
       <c r="F519" s="2"/>
       <c r="G519" s="14"/>
     </row>
-    <row r="520" spans="1:7" s="3" customFormat="1">
+    <row r="520" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="14"/>
@@ -6198,7 +6289,7 @@
       <c r="F520" s="2"/>
       <c r="G520" s="14"/>
     </row>
-    <row r="521" spans="1:7" s="3" customFormat="1">
+    <row r="521" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="14"/>
@@ -6207,7 +6298,7 @@
       <c r="F521" s="2"/>
       <c r="G521" s="14"/>
     </row>
-    <row r="522" spans="1:7" s="3" customFormat="1">
+    <row r="522" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="14"/>
@@ -6216,7 +6307,7 @@
       <c r="F522" s="2"/>
       <c r="G522" s="14"/>
     </row>
-    <row r="523" spans="1:7" s="3" customFormat="1">
+    <row r="523" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="14"/>
@@ -6225,7 +6316,7 @@
       <c r="F523" s="2"/>
       <c r="G523" s="14"/>
     </row>
-    <row r="524" spans="1:7" s="3" customFormat="1">
+    <row r="524" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="14"/>
@@ -6234,7 +6325,7 @@
       <c r="F524" s="2"/>
       <c r="G524" s="14"/>
     </row>
-    <row r="525" spans="1:7" s="3" customFormat="1">
+    <row r="525" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="14"/>
@@ -6243,7 +6334,7 @@
       <c r="F525" s="2"/>
       <c r="G525" s="14"/>
     </row>
-    <row r="526" spans="1:7" s="3" customFormat="1">
+    <row r="526" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="14"/>
@@ -6252,7 +6343,7 @@
       <c r="F526" s="2"/>
       <c r="G526" s="14"/>
     </row>
-    <row r="527" spans="1:7" s="3" customFormat="1">
+    <row r="527" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="14"/>
@@ -6261,7 +6352,7 @@
       <c r="F527" s="2"/>
       <c r="G527" s="14"/>
     </row>
-    <row r="528" spans="1:7" s="3" customFormat="1">
+    <row r="528" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="14"/>
@@ -6270,7 +6361,7 @@
       <c r="F528" s="2"/>
       <c r="G528" s="14"/>
     </row>
-    <row r="529" spans="1:7" s="3" customFormat="1">
+    <row r="529" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="14"/>
@@ -6279,7 +6370,7 @@
       <c r="F529" s="2"/>
       <c r="G529" s="14"/>
     </row>
-    <row r="530" spans="1:7" s="3" customFormat="1">
+    <row r="530" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="14"/>
@@ -6288,7 +6379,7 @@
       <c r="F530" s="2"/>
       <c r="G530" s="14"/>
     </row>
-    <row r="531" spans="1:7" s="3" customFormat="1">
+    <row r="531" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="14"/>
@@ -6297,7 +6388,7 @@
       <c r="F531" s="2"/>
       <c r="G531" s="14"/>
     </row>
-    <row r="532" spans="1:7" s="3" customFormat="1">
+    <row r="532" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="14"/>
@@ -6306,7 +6397,7 @@
       <c r="F532" s="2"/>
       <c r="G532" s="14"/>
     </row>
-    <row r="533" spans="1:7" s="3" customFormat="1">
+    <row r="533" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="14"/>
@@ -6315,7 +6406,7 @@
       <c r="F533" s="2"/>
       <c r="G533" s="14"/>
     </row>
-    <row r="534" spans="1:7" s="3" customFormat="1">
+    <row r="534" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="14"/>
@@ -6324,7 +6415,7 @@
       <c r="F534" s="2"/>
       <c r="G534" s="14"/>
     </row>
-    <row r="535" spans="1:7" s="3" customFormat="1">
+    <row r="535" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="14"/>
@@ -6333,7 +6424,7 @@
       <c r="F535" s="2"/>
       <c r="G535" s="14"/>
     </row>
-    <row r="536" spans="1:7" s="3" customFormat="1">
+    <row r="536" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="14"/>
@@ -6342,7 +6433,7 @@
       <c r="F536" s="2"/>
       <c r="G536" s="14"/>
     </row>
-    <row r="537" spans="1:7" s="3" customFormat="1">
+    <row r="537" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="14"/>
@@ -6351,7 +6442,7 @@
       <c r="F537" s="2"/>
       <c r="G537" s="14"/>
     </row>
-    <row r="538" spans="1:7" s="3" customFormat="1">
+    <row r="538" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="14"/>
@@ -6360,7 +6451,7 @@
       <c r="F538" s="2"/>
       <c r="G538" s="14"/>
     </row>
-    <row r="539" spans="1:7" s="3" customFormat="1">
+    <row r="539" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="14"/>
@@ -6369,7 +6460,7 @@
       <c r="F539" s="2"/>
       <c r="G539" s="14"/>
     </row>
-    <row r="540" spans="1:7" s="3" customFormat="1">
+    <row r="540" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="14"/>
@@ -6378,7 +6469,7 @@
       <c r="F540" s="2"/>
       <c r="G540" s="14"/>
     </row>
-    <row r="541" spans="1:7" s="3" customFormat="1">
+    <row r="541" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="14"/>
@@ -6387,7 +6478,7 @@
       <c r="F541" s="2"/>
       <c r="G541" s="14"/>
     </row>
-    <row r="542" spans="1:7" s="3" customFormat="1">
+    <row r="542" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="14"/>
@@ -6396,7 +6487,7 @@
       <c r="F542" s="2"/>
       <c r="G542" s="14"/>
     </row>
-    <row r="543" spans="1:7" s="3" customFormat="1">
+    <row r="543" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="14"/>
@@ -6405,7 +6496,7 @@
       <c r="F543" s="2"/>
       <c r="G543" s="14"/>
     </row>
-    <row r="544" spans="1:7" s="3" customFormat="1">
+    <row r="544" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="14"/>
@@ -6414,7 +6505,7 @@
       <c r="F544" s="2"/>
       <c r="G544" s="14"/>
     </row>
-    <row r="545" spans="1:7" s="3" customFormat="1">
+    <row r="545" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="14"/>
@@ -6423,7 +6514,7 @@
       <c r="F545" s="2"/>
       <c r="G545" s="14"/>
     </row>
-    <row r="546" spans="1:7" s="3" customFormat="1">
+    <row r="546" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="14"/>
@@ -6432,7 +6523,7 @@
       <c r="F546" s="2"/>
       <c r="G546" s="14"/>
     </row>
-    <row r="547" spans="1:7" s="3" customFormat="1">
+    <row r="547" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="14"/>
@@ -6441,7 +6532,7 @@
       <c r="F547" s="2"/>
       <c r="G547" s="14"/>
     </row>
-    <row r="548" spans="1:7" s="3" customFormat="1">
+    <row r="548" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="14"/>
@@ -6450,7 +6541,7 @@
       <c r="F548" s="2"/>
       <c r="G548" s="14"/>
     </row>
-    <row r="549" spans="1:7" s="3" customFormat="1">
+    <row r="549" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="14"/>
@@ -6459,7 +6550,7 @@
       <c r="F549" s="2"/>
       <c r="G549" s="14"/>
     </row>
-    <row r="550" spans="1:7" s="3" customFormat="1">
+    <row r="550" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="14"/>
@@ -6468,7 +6559,7 @@
       <c r="F550" s="2"/>
       <c r="G550" s="14"/>
     </row>
-    <row r="551" spans="1:7" s="3" customFormat="1">
+    <row r="551" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="14"/>
@@ -6477,7 +6568,7 @@
       <c r="F551" s="2"/>
       <c r="G551" s="14"/>
     </row>
-    <row r="552" spans="1:7" s="3" customFormat="1">
+    <row r="552" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="14"/>
@@ -6486,7 +6577,7 @@
       <c r="F552" s="2"/>
       <c r="G552" s="14"/>
     </row>
-    <row r="553" spans="1:7" s="3" customFormat="1">
+    <row r="553" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="14"/>
@@ -6495,7 +6586,7 @@
       <c r="F553" s="2"/>
       <c r="G553" s="14"/>
     </row>
-    <row r="554" spans="1:7" s="3" customFormat="1">
+    <row r="554" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="14"/>
@@ -6504,7 +6595,7 @@
       <c r="F554" s="2"/>
       <c r="G554" s="14"/>
     </row>
-    <row r="555" spans="1:7" s="3" customFormat="1">
+    <row r="555" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="14"/>
@@ -6513,7 +6604,7 @@
       <c r="F555" s="2"/>
       <c r="G555" s="14"/>
     </row>
-    <row r="556" spans="1:7" s="3" customFormat="1">
+    <row r="556" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="14"/>
@@ -6522,7 +6613,7 @@
       <c r="F556" s="2"/>
       <c r="G556" s="14"/>
     </row>
-    <row r="557" spans="1:7" s="3" customFormat="1">
+    <row r="557" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="14"/>
@@ -6531,7 +6622,7 @@
       <c r="F557" s="2"/>
       <c r="G557" s="14"/>
     </row>
-    <row r="558" spans="1:7" s="3" customFormat="1">
+    <row r="558" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="14"/>
@@ -6540,7 +6631,7 @@
       <c r="F558" s="2"/>
       <c r="G558" s="14"/>
     </row>
-    <row r="559" spans="1:7" s="3" customFormat="1">
+    <row r="559" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="14"/>
@@ -6549,7 +6640,7 @@
       <c r="F559" s="2"/>
       <c r="G559" s="14"/>
     </row>
-    <row r="560" spans="1:7" s="3" customFormat="1">
+    <row r="560" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="14"/>
@@ -6558,7 +6649,7 @@
       <c r="F560" s="2"/>
       <c r="G560" s="14"/>
     </row>
-    <row r="561" spans="1:7" s="3" customFormat="1">
+    <row r="561" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="14"/>
@@ -6567,7 +6658,7 @@
       <c r="F561" s="2"/>
       <c r="G561" s="14"/>
     </row>
-    <row r="562" spans="1:7" s="3" customFormat="1">
+    <row r="562" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="14"/>
@@ -6576,7 +6667,7 @@
       <c r="F562" s="2"/>
       <c r="G562" s="14"/>
     </row>
-    <row r="563" spans="1:7" s="3" customFormat="1">
+    <row r="563" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="14"/>
@@ -6585,7 +6676,7 @@
       <c r="F563" s="2"/>
       <c r="G563" s="14"/>
     </row>
-    <row r="564" spans="1:7" s="3" customFormat="1">
+    <row r="564" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="14"/>
@@ -6594,7 +6685,7 @@
       <c r="F564" s="2"/>
       <c r="G564" s="14"/>
     </row>
-    <row r="565" spans="1:7" s="3" customFormat="1">
+    <row r="565" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="14"/>
@@ -6603,7 +6694,7 @@
       <c r="F565" s="2"/>
       <c r="G565" s="14"/>
     </row>
-    <row r="566" spans="1:7" s="3" customFormat="1">
+    <row r="566" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="14"/>
@@ -6612,7 +6703,7 @@
       <c r="F566" s="2"/>
       <c r="G566" s="14"/>
     </row>
-    <row r="567" spans="1:7" s="3" customFormat="1">
+    <row r="567" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="14"/>
@@ -6621,7 +6712,7 @@
       <c r="F567" s="2"/>
       <c r="G567" s="14"/>
     </row>
-    <row r="568" spans="1:7" s="3" customFormat="1">
+    <row r="568" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="14"/>
@@ -6630,7 +6721,7 @@
       <c r="F568" s="2"/>
       <c r="G568" s="14"/>
     </row>
-    <row r="569" spans="1:7" s="3" customFormat="1">
+    <row r="569" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="14"/>
@@ -6639,7 +6730,7 @@
       <c r="F569" s="2"/>
       <c r="G569" s="14"/>
     </row>
-    <row r="570" spans="1:7" s="3" customFormat="1">
+    <row r="570" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="14"/>
@@ -6648,7 +6739,7 @@
       <c r="F570" s="2"/>
       <c r="G570" s="14"/>
     </row>
-    <row r="571" spans="1:7" s="3" customFormat="1">
+    <row r="571" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="14"/>
@@ -6657,7 +6748,7 @@
       <c r="F571" s="2"/>
       <c r="G571" s="14"/>
     </row>
-    <row r="572" spans="1:7" s="3" customFormat="1">
+    <row r="572" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="14"/>
@@ -6666,7 +6757,7 @@
       <c r="F572" s="2"/>
       <c r="G572" s="14"/>
     </row>
-    <row r="573" spans="1:7" s="3" customFormat="1">
+    <row r="573" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="14"/>
@@ -6675,7 +6766,7 @@
       <c r="F573" s="2"/>
       <c r="G573" s="14"/>
     </row>
-    <row r="574" spans="1:7" s="3" customFormat="1">
+    <row r="574" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="14"/>
@@ -6684,7 +6775,7 @@
       <c r="F574" s="2"/>
       <c r="G574" s="14"/>
     </row>
-    <row r="575" spans="1:7" s="3" customFormat="1">
+    <row r="575" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="14"/>
@@ -6693,7 +6784,7 @@
       <c r="F575" s="2"/>
       <c r="G575" s="14"/>
     </row>
-    <row r="576" spans="1:7" s="3" customFormat="1">
+    <row r="576" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="14"/>
@@ -6702,7 +6793,7 @@
       <c r="F576" s="2"/>
       <c r="G576" s="14"/>
     </row>
-    <row r="577" spans="1:7" s="3" customFormat="1">
+    <row r="577" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="14"/>
@@ -6711,7 +6802,7 @@
       <c r="F577" s="2"/>
       <c r="G577" s="14"/>
     </row>
-    <row r="578" spans="1:7" s="3" customFormat="1">
+    <row r="578" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="14"/>
@@ -6720,7 +6811,7 @@
       <c r="F578" s="2"/>
       <c r="G578" s="14"/>
     </row>
-    <row r="579" spans="1:7" s="3" customFormat="1">
+    <row r="579" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="14"/>
@@ -6729,7 +6820,7 @@
       <c r="F579" s="2"/>
       <c r="G579" s="14"/>
     </row>
-    <row r="580" spans="1:7" s="3" customFormat="1">
+    <row r="580" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="14"/>
@@ -6738,7 +6829,7 @@
       <c r="F580" s="2"/>
       <c r="G580" s="14"/>
     </row>
-    <row r="581" spans="1:7" s="3" customFormat="1">
+    <row r="581" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="14"/>
@@ -6747,7 +6838,7 @@
       <c r="F581" s="2"/>
       <c r="G581" s="14"/>
     </row>
-    <row r="582" spans="1:7" s="3" customFormat="1">
+    <row r="582" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="14"/>
@@ -6756,7 +6847,7 @@
       <c r="F582" s="2"/>
       <c r="G582" s="14"/>
     </row>
-    <row r="583" spans="1:7" s="3" customFormat="1">
+    <row r="583" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="14"/>
@@ -6765,7 +6856,7 @@
       <c r="F583" s="2"/>
       <c r="G583" s="14"/>
     </row>
-    <row r="584" spans="1:7" s="3" customFormat="1">
+    <row r="584" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="14"/>
@@ -6774,7 +6865,7 @@
       <c r="F584" s="2"/>
       <c r="G584" s="14"/>
     </row>
-    <row r="585" spans="1:7" s="3" customFormat="1">
+    <row r="585" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="14"/>
@@ -6783,7 +6874,7 @@
       <c r="F585" s="2"/>
       <c r="G585" s="14"/>
     </row>
-    <row r="586" spans="1:7" s="3" customFormat="1">
+    <row r="586" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="14"/>
@@ -6792,7 +6883,7 @@
       <c r="F586" s="2"/>
       <c r="G586" s="14"/>
     </row>
-    <row r="587" spans="1:7" s="3" customFormat="1">
+    <row r="587" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="14"/>
@@ -6801,7 +6892,7 @@
       <c r="F587" s="2"/>
       <c r="G587" s="14"/>
     </row>
-    <row r="588" spans="1:7" s="3" customFormat="1">
+    <row r="588" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="14"/>
@@ -6810,7 +6901,7 @@
       <c r="F588" s="2"/>
       <c r="G588" s="14"/>
     </row>
-    <row r="589" spans="1:7" s="3" customFormat="1">
+    <row r="589" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="14"/>
@@ -6819,7 +6910,7 @@
       <c r="F589" s="2"/>
       <c r="G589" s="14"/>
     </row>
-    <row r="590" spans="1:7" s="3" customFormat="1">
+    <row r="590" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="14"/>
@@ -6828,7 +6919,7 @@
       <c r="F590" s="2"/>
       <c r="G590" s="14"/>
     </row>
-    <row r="591" spans="1:7" s="3" customFormat="1">
+    <row r="591" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="14"/>
@@ -6837,7 +6928,7 @@
       <c r="F591" s="2"/>
       <c r="G591" s="14"/>
     </row>
-    <row r="592" spans="1:7" s="3" customFormat="1">
+    <row r="592" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="14"/>
@@ -6846,7 +6937,7 @@
       <c r="F592" s="2"/>
       <c r="G592" s="14"/>
     </row>
-    <row r="593" spans="1:7" s="3" customFormat="1">
+    <row r="593" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="14"/>
@@ -6855,7 +6946,7 @@
       <c r="F593" s="2"/>
       <c r="G593" s="14"/>
     </row>
-    <row r="594" spans="1:7" s="3" customFormat="1">
+    <row r="594" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="14"/>
@@ -6864,7 +6955,7 @@
       <c r="F594" s="2"/>
       <c r="G594" s="14"/>
     </row>
-    <row r="595" spans="1:7" s="3" customFormat="1">
+    <row r="595" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="14"/>
@@ -6873,7 +6964,7 @@
       <c r="F595" s="2"/>
       <c r="G595" s="14"/>
     </row>
-    <row r="596" spans="1:7" s="3" customFormat="1">
+    <row r="596" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="14"/>
@@ -6882,7 +6973,7 @@
       <c r="F596" s="2"/>
       <c r="G596" s="14"/>
     </row>
-    <row r="597" spans="1:7" s="3" customFormat="1">
+    <row r="597" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="14"/>
@@ -6891,7 +6982,7 @@
       <c r="F597" s="2"/>
       <c r="G597" s="14"/>
     </row>
-    <row r="598" spans="1:7" s="3" customFormat="1">
+    <row r="598" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="14"/>
@@ -6900,7 +6991,7 @@
       <c r="F598" s="2"/>
       <c r="G598" s="14"/>
     </row>
-    <row r="599" spans="1:7" s="3" customFormat="1">
+    <row r="599" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="14"/>
@@ -6909,7 +7000,7 @@
       <c r="F599" s="2"/>
       <c r="G599" s="14"/>
     </row>
-    <row r="600" spans="1:7" s="3" customFormat="1">
+    <row r="600" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="14"/>
@@ -6918,7 +7009,7 @@
       <c r="F600" s="2"/>
       <c r="G600" s="14"/>
     </row>
-    <row r="601" spans="1:7" s="3" customFormat="1">
+    <row r="601" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="14"/>
@@ -6927,7 +7018,7 @@
       <c r="F601" s="2"/>
       <c r="G601" s="14"/>
     </row>
-    <row r="602" spans="1:7" s="3" customFormat="1">
+    <row r="602" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="14"/>
@@ -6936,7 +7027,7 @@
       <c r="F602" s="2"/>
       <c r="G602" s="14"/>
     </row>
-    <row r="603" spans="1:7" s="3" customFormat="1">
+    <row r="603" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="14"/>
@@ -6945,7 +7036,7 @@
       <c r="F603" s="2"/>
       <c r="G603" s="14"/>
     </row>
-    <row r="604" spans="1:7" s="3" customFormat="1">
+    <row r="604" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="14"/>
@@ -6954,7 +7045,7 @@
       <c r="F604" s="2"/>
       <c r="G604" s="14"/>
     </row>
-    <row r="605" spans="1:7" s="3" customFormat="1">
+    <row r="605" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="14"/>
@@ -6963,7 +7054,7 @@
       <c r="F605" s="2"/>
       <c r="G605" s="14"/>
     </row>
-    <row r="606" spans="1:7" s="3" customFormat="1">
+    <row r="606" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="14"/>
@@ -6972,7 +7063,7 @@
       <c r="F606" s="2"/>
       <c r="G606" s="14"/>
     </row>
-    <row r="607" spans="1:7" s="3" customFormat="1">
+    <row r="607" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="14"/>
@@ -6981,7 +7072,7 @@
       <c r="F607" s="2"/>
       <c r="G607" s="14"/>
     </row>
-    <row r="608" spans="1:7" s="3" customFormat="1">
+    <row r="608" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="14"/>
@@ -6990,7 +7081,7 @@
       <c r="F608" s="2"/>
       <c r="G608" s="14"/>
     </row>
-    <row r="609" spans="1:7" s="3" customFormat="1">
+    <row r="609" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="14"/>
@@ -6999,7 +7090,7 @@
       <c r="F609" s="2"/>
       <c r="G609" s="14"/>
     </row>
-    <row r="610" spans="1:7" s="3" customFormat="1">
+    <row r="610" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="14"/>
@@ -7008,7 +7099,7 @@
       <c r="F610" s="2"/>
       <c r="G610" s="14"/>
     </row>
-    <row r="611" spans="1:7" s="3" customFormat="1">
+    <row r="611" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="14"/>
@@ -7017,7 +7108,7 @@
       <c r="F611" s="2"/>
       <c r="G611" s="14"/>
     </row>
-    <row r="612" spans="1:7" s="3" customFormat="1">
+    <row r="612" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="14"/>
@@ -7026,7 +7117,7 @@
       <c r="F612" s="2"/>
       <c r="G612" s="14"/>
     </row>
-    <row r="613" spans="1:7" s="3" customFormat="1">
+    <row r="613" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="14"/>
@@ -7035,7 +7126,7 @@
       <c r="F613" s="2"/>
       <c r="G613" s="14"/>
     </row>
-    <row r="614" spans="1:7" s="3" customFormat="1">
+    <row r="614" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="14"/>
@@ -7044,7 +7135,7 @@
       <c r="F614" s="2"/>
       <c r="G614" s="14"/>
     </row>
-    <row r="615" spans="1:7" s="3" customFormat="1">
+    <row r="615" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="14"/>
@@ -7053,7 +7144,7 @@
       <c r="F615" s="2"/>
       <c r="G615" s="14"/>
     </row>
-    <row r="616" spans="1:7" s="3" customFormat="1">
+    <row r="616" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="14"/>
@@ -7062,7 +7153,7 @@
       <c r="F616" s="2"/>
       <c r="G616" s="14"/>
     </row>
-    <row r="617" spans="1:7" s="3" customFormat="1">
+    <row r="617" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="14"/>
@@ -7071,7 +7162,7 @@
       <c r="F617" s="2"/>
       <c r="G617" s="14"/>
     </row>
-    <row r="618" spans="1:7" s="3" customFormat="1">
+    <row r="618" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="14"/>
@@ -7080,7 +7171,7 @@
       <c r="F618" s="2"/>
       <c r="G618" s="14"/>
     </row>
-    <row r="619" spans="1:7" s="3" customFormat="1">
+    <row r="619" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="14"/>
@@ -7089,7 +7180,7 @@
       <c r="F619" s="2"/>
       <c r="G619" s="14"/>
     </row>
-    <row r="620" spans="1:7" s="3" customFormat="1">
+    <row r="620" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="14"/>
@@ -7098,7 +7189,7 @@
       <c r="F620" s="2"/>
       <c r="G620" s="14"/>
     </row>
-    <row r="621" spans="1:7" s="3" customFormat="1">
+    <row r="621" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="14"/>
@@ -7107,7 +7198,7 @@
       <c r="F621" s="2"/>
       <c r="G621" s="14"/>
     </row>
-    <row r="622" spans="1:7" s="3" customFormat="1">
+    <row r="622" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="14"/>
@@ -7116,7 +7207,7 @@
       <c r="F622" s="2"/>
       <c r="G622" s="14"/>
     </row>
-    <row r="623" spans="1:7" s="3" customFormat="1">
+    <row r="623" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="14"/>
@@ -7125,7 +7216,7 @@
       <c r="F623" s="2"/>
       <c r="G623" s="14"/>
     </row>
-    <row r="624" spans="1:7" s="3" customFormat="1">
+    <row r="624" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="14"/>
@@ -7134,7 +7225,7 @@
       <c r="F624" s="2"/>
       <c r="G624" s="14"/>
     </row>
-    <row r="625" spans="1:7" s="3" customFormat="1">
+    <row r="625" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="14"/>
@@ -7143,7 +7234,7 @@
       <c r="F625" s="2"/>
       <c r="G625" s="14"/>
     </row>
-    <row r="626" spans="1:7" s="3" customFormat="1">
+    <row r="626" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="14"/>
@@ -7152,7 +7243,7 @@
       <c r="F626" s="2"/>
       <c r="G626" s="14"/>
     </row>
-    <row r="627" spans="1:7" s="3" customFormat="1">
+    <row r="627" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="14"/>
@@ -7161,7 +7252,7 @@
       <c r="F627" s="2"/>
       <c r="G627" s="14"/>
     </row>
-    <row r="628" spans="1:7" s="3" customFormat="1">
+    <row r="628" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="14"/>
@@ -7170,7 +7261,7 @@
       <c r="F628" s="2"/>
       <c r="G628" s="14"/>
     </row>
-    <row r="629" spans="1:7" s="3" customFormat="1">
+    <row r="629" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="14"/>
@@ -7179,7 +7270,7 @@
       <c r="F629" s="2"/>
       <c r="G629" s="14"/>
     </row>
-    <row r="630" spans="1:7" s="3" customFormat="1">
+    <row r="630" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="14"/>
@@ -7188,7 +7279,7 @@
       <c r="F630" s="2"/>
       <c r="G630" s="14"/>
     </row>
-    <row r="631" spans="1:7" s="3" customFormat="1">
+    <row r="631" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="14"/>
@@ -7197,7 +7288,7 @@
       <c r="F631" s="2"/>
       <c r="G631" s="14"/>
     </row>
-    <row r="632" spans="1:7" s="3" customFormat="1">
+    <row r="632" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="14"/>
@@ -7206,7 +7297,7 @@
       <c r="F632" s="2"/>
       <c r="G632" s="14"/>
     </row>
-    <row r="633" spans="1:7" s="3" customFormat="1">
+    <row r="633" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="14"/>
@@ -7215,7 +7306,7 @@
       <c r="F633" s="2"/>
       <c r="G633" s="14"/>
     </row>
-    <row r="634" spans="1:7" s="3" customFormat="1">
+    <row r="634" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="14"/>
@@ -7224,7 +7315,7 @@
       <c r="F634" s="2"/>
       <c r="G634" s="14"/>
     </row>
-    <row r="635" spans="1:7" s="3" customFormat="1">
+    <row r="635" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="14"/>
@@ -7233,7 +7324,7 @@
       <c r="F635" s="2"/>
       <c r="G635" s="14"/>
     </row>
-    <row r="636" spans="1:7" s="3" customFormat="1">
+    <row r="636" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="14"/>
@@ -7242,7 +7333,7 @@
       <c r="F636" s="2"/>
       <c r="G636" s="14"/>
     </row>
-    <row r="637" spans="1:7" s="3" customFormat="1">
+    <row r="637" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="14"/>
@@ -7251,7 +7342,7 @@
       <c r="F637" s="2"/>
       <c r="G637" s="14"/>
     </row>
-    <row r="638" spans="1:7" s="3" customFormat="1">
+    <row r="638" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="14"/>
@@ -7260,7 +7351,7 @@
       <c r="F638" s="2"/>
       <c r="G638" s="14"/>
     </row>
-    <row r="639" spans="1:7" s="3" customFormat="1">
+    <row r="639" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="14"/>
@@ -7269,7 +7360,7 @@
       <c r="F639" s="2"/>
       <c r="G639" s="14"/>
     </row>
-    <row r="640" spans="1:7" s="3" customFormat="1">
+    <row r="640" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="14"/>
@@ -7278,7 +7369,7 @@
       <c r="F640" s="2"/>
       <c r="G640" s="14"/>
     </row>
-    <row r="641" spans="1:7" s="3" customFormat="1">
+    <row r="641" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="14"/>
@@ -7287,7 +7378,7 @@
       <c r="F641" s="2"/>
       <c r="G641" s="14"/>
     </row>
-    <row r="642" spans="1:7" s="3" customFormat="1">
+    <row r="642" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="14"/>
@@ -7296,7 +7387,7 @@
       <c r="F642" s="2"/>
       <c r="G642" s="14"/>
     </row>
-    <row r="643" spans="1:7" s="3" customFormat="1">
+    <row r="643" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="14"/>
@@ -7305,7 +7396,7 @@
       <c r="F643" s="2"/>
       <c r="G643" s="14"/>
     </row>
-    <row r="644" spans="1:7" s="3" customFormat="1">
+    <row r="644" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="14"/>
@@ -7314,7 +7405,7 @@
       <c r="F644" s="2"/>
       <c r="G644" s="14"/>
     </row>
-    <row r="645" spans="1:7" s="3" customFormat="1">
+    <row r="645" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="14"/>
@@ -7323,7 +7414,7 @@
       <c r="F645" s="2"/>
       <c r="G645" s="14"/>
     </row>
-    <row r="646" spans="1:7" s="3" customFormat="1">
+    <row r="646" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="14"/>
@@ -7332,7 +7423,7 @@
       <c r="F646" s="2"/>
       <c r="G646" s="14"/>
     </row>
-    <row r="647" spans="1:7" s="3" customFormat="1">
+    <row r="647" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="14"/>
@@ -7341,7 +7432,7 @@
       <c r="F647" s="2"/>
       <c r="G647" s="14"/>
     </row>
-    <row r="648" spans="1:7" s="3" customFormat="1">
+    <row r="648" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="14"/>
@@ -7350,7 +7441,7 @@
       <c r="F648" s="2"/>
       <c r="G648" s="14"/>
     </row>
-    <row r="649" spans="1:7" s="3" customFormat="1">
+    <row r="649" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="14"/>
@@ -7359,7 +7450,7 @@
       <c r="F649" s="2"/>
       <c r="G649" s="14"/>
     </row>
-    <row r="650" spans="1:7" s="3" customFormat="1">
+    <row r="650" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="14"/>
@@ -7368,7 +7459,7 @@
       <c r="F650" s="2"/>
       <c r="G650" s="14"/>
     </row>
-    <row r="651" spans="1:7" s="3" customFormat="1">
+    <row r="651" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="14"/>
@@ -7377,7 +7468,7 @@
       <c r="F651" s="2"/>
       <c r="G651" s="14"/>
     </row>
-    <row r="652" spans="1:7" s="3" customFormat="1">
+    <row r="652" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="14"/>
@@ -7386,7 +7477,7 @@
       <c r="F652" s="2"/>
       <c r="G652" s="14"/>
     </row>
-    <row r="653" spans="1:7" s="3" customFormat="1">
+    <row r="653" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="14"/>
@@ -7395,7 +7486,7 @@
       <c r="F653" s="2"/>
       <c r="G653" s="14"/>
     </row>
-    <row r="654" spans="1:7" s="3" customFormat="1">
+    <row r="654" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="14"/>
@@ -7404,7 +7495,7 @@
       <c r="F654" s="2"/>
       <c r="G654" s="14"/>
     </row>
-    <row r="655" spans="1:7" s="3" customFormat="1">
+    <row r="655" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="14"/>
@@ -7413,7 +7504,7 @@
       <c r="F655" s="2"/>
       <c r="G655" s="14"/>
     </row>
-    <row r="656" spans="1:7" s="3" customFormat="1">
+    <row r="656" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="14"/>
@@ -7422,7 +7513,7 @@
       <c r="F656" s="2"/>
       <c r="G656" s="14"/>
     </row>
-    <row r="657" spans="1:7" s="3" customFormat="1">
+    <row r="657" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="14"/>
@@ -7431,7 +7522,7 @@
       <c r="F657" s="2"/>
       <c r="G657" s="14"/>
     </row>
-    <row r="658" spans="1:7" s="3" customFormat="1">
+    <row r="658" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="14"/>
@@ -7440,7 +7531,7 @@
       <c r="F658" s="2"/>
       <c r="G658" s="14"/>
     </row>
-    <row r="659" spans="1:7" s="3" customFormat="1">
+    <row r="659" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="14"/>
@@ -7449,7 +7540,7 @@
       <c r="F659" s="2"/>
       <c r="G659" s="14"/>
     </row>
-    <row r="660" spans="1:7" s="3" customFormat="1">
+    <row r="660" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="14"/>
@@ -7458,7 +7549,7 @@
       <c r="F660" s="2"/>
       <c r="G660" s="14"/>
     </row>
-    <row r="661" spans="1:7" s="3" customFormat="1">
+    <row r="661" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="14"/>
@@ -7467,7 +7558,7 @@
       <c r="F661" s="2"/>
       <c r="G661" s="14"/>
     </row>
-    <row r="662" spans="1:7" s="3" customFormat="1">
+    <row r="662" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="14"/>
@@ -7476,7 +7567,7 @@
       <c r="F662" s="2"/>
       <c r="G662" s="14"/>
     </row>
-    <row r="663" spans="1:7" s="3" customFormat="1">
+    <row r="663" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="14"/>
@@ -7485,7 +7576,7 @@
       <c r="F663" s="2"/>
       <c r="G663" s="14"/>
     </row>
-    <row r="664" spans="1:7" s="3" customFormat="1">
+    <row r="664" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="14"/>
@@ -7494,7 +7585,7 @@
       <c r="F664" s="2"/>
       <c r="G664" s="14"/>
     </row>
-    <row r="665" spans="1:7" s="3" customFormat="1">
+    <row r="665" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="14"/>
@@ -7503,7 +7594,7 @@
       <c r="F665" s="2"/>
       <c r="G665" s="14"/>
     </row>
-    <row r="666" spans="1:7" s="3" customFormat="1">
+    <row r="666" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="14"/>
@@ -7512,7 +7603,7 @@
       <c r="F666" s="2"/>
       <c r="G666" s="14"/>
     </row>
-    <row r="667" spans="1:7" s="3" customFormat="1">
+    <row r="667" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="14"/>
@@ -7521,7 +7612,7 @@
       <c r="F667" s="2"/>
       <c r="G667" s="14"/>
     </row>
-    <row r="668" spans="1:7" s="3" customFormat="1">
+    <row r="668" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="14"/>
@@ -7530,7 +7621,7 @@
       <c r="F668" s="2"/>
       <c r="G668" s="14"/>
     </row>
-    <row r="669" spans="1:7" s="3" customFormat="1">
+    <row r="669" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="14"/>
@@ -7539,7 +7630,7 @@
       <c r="F669" s="2"/>
       <c r="G669" s="14"/>
     </row>
-    <row r="670" spans="1:7" s="3" customFormat="1">
+    <row r="670" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="14"/>
@@ -7548,7 +7639,7 @@
       <c r="F670" s="2"/>
       <c r="G670" s="14"/>
     </row>
-    <row r="671" spans="1:7" s="3" customFormat="1">
+    <row r="671" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="14"/>
@@ -7557,7 +7648,7 @@
       <c r="F671" s="2"/>
       <c r="G671" s="14"/>
     </row>
-    <row r="672" spans="1:7" s="3" customFormat="1">
+    <row r="672" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="14"/>
@@ -7566,7 +7657,7 @@
       <c r="F672" s="2"/>
       <c r="G672" s="14"/>
     </row>
-    <row r="673" spans="1:7" s="3" customFormat="1">
+    <row r="673" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="14"/>
@@ -7575,7 +7666,7 @@
       <c r="F673" s="2"/>
       <c r="G673" s="14"/>
     </row>
-    <row r="674" spans="1:7" s="3" customFormat="1">
+    <row r="674" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="14"/>
@@ -7584,7 +7675,7 @@
       <c r="F674" s="2"/>
       <c r="G674" s="14"/>
     </row>
-    <row r="675" spans="1:7" s="3" customFormat="1">
+    <row r="675" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="14"/>
@@ -7593,7 +7684,7 @@
       <c r="F675" s="2"/>
       <c r="G675" s="14"/>
     </row>
-    <row r="676" spans="1:7" s="3" customFormat="1">
+    <row r="676" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="14"/>
@@ -7602,7 +7693,7 @@
       <c r="F676" s="2"/>
       <c r="G676" s="14"/>
     </row>
-    <row r="677" spans="1:7" s="3" customFormat="1">
+    <row r="677" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="14"/>
@@ -7611,7 +7702,7 @@
       <c r="F677" s="2"/>
       <c r="G677" s="14"/>
     </row>
-    <row r="678" spans="1:7" s="3" customFormat="1">
+    <row r="678" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="14"/>
@@ -7620,7 +7711,7 @@
       <c r="F678" s="2"/>
       <c r="G678" s="14"/>
     </row>
-    <row r="679" spans="1:7" s="3" customFormat="1">
+    <row r="679" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="14"/>
@@ -7629,7 +7720,7 @@
       <c r="F679" s="2"/>
       <c r="G679" s="14"/>
     </row>
-    <row r="680" spans="1:7" s="3" customFormat="1">
+    <row r="680" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="14"/>
@@ -7638,7 +7729,7 @@
       <c r="F680" s="2"/>
       <c r="G680" s="14"/>
     </row>
-    <row r="681" spans="1:7" s="3" customFormat="1">
+    <row r="681" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="14"/>
@@ -7647,7 +7738,7 @@
       <c r="F681" s="2"/>
       <c r="G681" s="14"/>
     </row>
-    <row r="682" spans="1:7" s="3" customFormat="1">
+    <row r="682" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="14"/>
@@ -7656,7 +7747,7 @@
       <c r="F682" s="2"/>
       <c r="G682" s="14"/>
     </row>
-    <row r="683" spans="1:7" s="3" customFormat="1">
+    <row r="683" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="14"/>
@@ -7665,7 +7756,7 @@
       <c r="F683" s="2"/>
       <c r="G683" s="14"/>
     </row>
-    <row r="684" spans="1:7" s="3" customFormat="1">
+    <row r="684" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="14"/>
@@ -7674,7 +7765,7 @@
       <c r="F684" s="2"/>
       <c r="G684" s="14"/>
     </row>
-    <row r="685" spans="1:7" s="3" customFormat="1">
+    <row r="685" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="14"/>
@@ -7683,7 +7774,7 @@
       <c r="F685" s="2"/>
       <c r="G685" s="14"/>
     </row>
-    <row r="686" spans="1:7" s="3" customFormat="1">
+    <row r="686" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="14"/>
@@ -7692,7 +7783,7 @@
       <c r="F686" s="2"/>
       <c r="G686" s="14"/>
     </row>
-    <row r="687" spans="1:7" s="3" customFormat="1">
+    <row r="687" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="14"/>
@@ -7701,7 +7792,7 @@
       <c r="F687" s="2"/>
       <c r="G687" s="14"/>
     </row>
-    <row r="688" spans="1:7" s="3" customFormat="1">
+    <row r="688" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="14"/>
@@ -7710,7 +7801,7 @@
       <c r="F688" s="2"/>
       <c r="G688" s="14"/>
     </row>
-    <row r="689" spans="1:7" s="3" customFormat="1">
+    <row r="689" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="14"/>
@@ -7719,7 +7810,7 @@
       <c r="F689" s="2"/>
       <c r="G689" s="14"/>
     </row>
-    <row r="690" spans="1:7" s="3" customFormat="1">
+    <row r="690" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="14"/>
@@ -7728,7 +7819,7 @@
       <c r="F690" s="2"/>
       <c r="G690" s="14"/>
     </row>
-    <row r="691" spans="1:7" s="3" customFormat="1">
+    <row r="691" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="14"/>
@@ -7737,7 +7828,7 @@
       <c r="F691" s="2"/>
       <c r="G691" s="14"/>
     </row>
-    <row r="692" spans="1:7" s="3" customFormat="1">
+    <row r="692" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="14"/>
@@ -7746,7 +7837,7 @@
       <c r="F692" s="2"/>
       <c r="G692" s="14"/>
     </row>
-    <row r="693" spans="1:7" s="3" customFormat="1">
+    <row r="693" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="14"/>
@@ -7755,7 +7846,7 @@
       <c r="F693" s="2"/>
       <c r="G693" s="14"/>
     </row>
-    <row r="694" spans="1:7" s="3" customFormat="1">
+    <row r="694" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="14"/>
@@ -7764,7 +7855,7 @@
       <c r="F694" s="2"/>
       <c r="G694" s="14"/>
     </row>
-    <row r="695" spans="1:7" s="3" customFormat="1">
+    <row r="695" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="14"/>
@@ -7773,7 +7864,7 @@
       <c r="F695" s="2"/>
       <c r="G695" s="14"/>
     </row>
-    <row r="696" spans="1:7" s="3" customFormat="1">
+    <row r="696" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="14"/>
@@ -7782,7 +7873,7 @@
       <c r="F696" s="2"/>
       <c r="G696" s="14"/>
     </row>
-    <row r="697" spans="1:7" s="3" customFormat="1">
+    <row r="697" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="14"/>
@@ -7791,7 +7882,7 @@
       <c r="F697" s="2"/>
       <c r="G697" s="14"/>
     </row>
-    <row r="698" spans="1:7" s="3" customFormat="1">
+    <row r="698" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="14"/>
@@ -7800,7 +7891,7 @@
       <c r="F698" s="2"/>
       <c r="G698" s="14"/>
     </row>
-    <row r="699" spans="1:7" s="3" customFormat="1">
+    <row r="699" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="14"/>
@@ -7809,7 +7900,7 @@
       <c r="F699" s="2"/>
       <c r="G699" s="14"/>
     </row>
-    <row r="700" spans="1:7" s="3" customFormat="1">
+    <row r="700" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="14"/>
@@ -7818,7 +7909,7 @@
       <c r="F700" s="2"/>
       <c r="G700" s="14"/>
     </row>
-    <row r="701" spans="1:7" s="3" customFormat="1">
+    <row r="701" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="14"/>
@@ -7827,7 +7918,7 @@
       <c r="F701" s="2"/>
       <c r="G701" s="14"/>
     </row>
-    <row r="702" spans="1:7" s="3" customFormat="1">
+    <row r="702" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="14"/>
@@ -7836,7 +7927,7 @@
       <c r="F702" s="2"/>
       <c r="G702" s="14"/>
     </row>
-    <row r="703" spans="1:7" s="3" customFormat="1">
+    <row r="703" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="14"/>
@@ -7845,7 +7936,7 @@
       <c r="F703" s="2"/>
       <c r="G703" s="14"/>
     </row>
-    <row r="704" spans="1:7" s="3" customFormat="1">
+    <row r="704" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="14"/>
@@ -7854,7 +7945,7 @@
       <c r="F704" s="2"/>
       <c r="G704" s="14"/>
     </row>
-    <row r="705" spans="1:7" s="3" customFormat="1">
+    <row r="705" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="14"/>
@@ -7863,7 +7954,7 @@
       <c r="F705" s="2"/>
       <c r="G705" s="14"/>
     </row>
-    <row r="706" spans="1:7" s="3" customFormat="1">
+    <row r="706" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="14"/>
@@ -7872,7 +7963,7 @@
       <c r="F706" s="2"/>
       <c r="G706" s="14"/>
     </row>
-    <row r="707" spans="1:7" s="3" customFormat="1">
+    <row r="707" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="14"/>
@@ -7881,7 +7972,7 @@
       <c r="F707" s="2"/>
       <c r="G707" s="14"/>
     </row>
-    <row r="708" spans="1:7" s="3" customFormat="1">
+    <row r="708" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="14"/>
@@ -7890,7 +7981,7 @@
       <c r="F708" s="2"/>
       <c r="G708" s="14"/>
     </row>
-    <row r="709" spans="1:7" s="3" customFormat="1">
+    <row r="709" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="14"/>
@@ -7899,7 +7990,7 @@
       <c r="F709" s="2"/>
       <c r="G709" s="14"/>
     </row>
-    <row r="710" spans="1:7" s="3" customFormat="1">
+    <row r="710" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="14"/>
@@ -7908,7 +7999,7 @@
       <c r="F710" s="2"/>
       <c r="G710" s="14"/>
     </row>
-    <row r="711" spans="1:7" s="3" customFormat="1">
+    <row r="711" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="14"/>
@@ -7917,7 +8008,7 @@
       <c r="F711" s="2"/>
       <c r="G711" s="14"/>
     </row>
-    <row r="712" spans="1:7" s="3" customFormat="1">
+    <row r="712" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="14"/>
@@ -7926,7 +8017,7 @@
       <c r="F712" s="2"/>
       <c r="G712" s="14"/>
     </row>
-    <row r="713" spans="1:7" s="3" customFormat="1">
+    <row r="713" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="14"/>
@@ -7935,7 +8026,7 @@
       <c r="F713" s="2"/>
       <c r="G713" s="14"/>
     </row>
-    <row r="714" spans="1:7" s="3" customFormat="1">
+    <row r="714" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="14"/>
@@ -7944,7 +8035,7 @@
       <c r="F714" s="2"/>
       <c r="G714" s="14"/>
     </row>
-    <row r="715" spans="1:7" s="3" customFormat="1">
+    <row r="715" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="14"/>
@@ -7953,7 +8044,7 @@
       <c r="F715" s="2"/>
       <c r="G715" s="14"/>
     </row>
-    <row r="716" spans="1:7" s="3" customFormat="1">
+    <row r="716" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="14"/>
@@ -7962,7 +8053,7 @@
       <c r="F716" s="2"/>
       <c r="G716" s="14"/>
     </row>
-    <row r="717" spans="1:7" s="3" customFormat="1">
+    <row r="717" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="14"/>
@@ -7971,7 +8062,7 @@
       <c r="F717" s="2"/>
       <c r="G717" s="14"/>
     </row>
-    <row r="718" spans="1:7" s="3" customFormat="1">
+    <row r="718" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="14"/>
@@ -7980,7 +8071,7 @@
       <c r="F718" s="2"/>
       <c r="G718" s="14"/>
     </row>
-    <row r="719" spans="1:7" s="3" customFormat="1">
+    <row r="719" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="14"/>
@@ -7989,7 +8080,7 @@
       <c r="F719" s="2"/>
       <c r="G719" s="14"/>
     </row>
-    <row r="720" spans="1:7" s="3" customFormat="1">
+    <row r="720" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="14"/>
@@ -7998,7 +8089,7 @@
       <c r="F720" s="2"/>
       <c r="G720" s="14"/>
     </row>
-    <row r="721" spans="1:7" s="3" customFormat="1">
+    <row r="721" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="14"/>
@@ -8007,7 +8098,7 @@
       <c r="F721" s="2"/>
       <c r="G721" s="14"/>
     </row>
-    <row r="722" spans="1:7" s="3" customFormat="1">
+    <row r="722" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="14"/>
@@ -8016,7 +8107,7 @@
       <c r="F722" s="2"/>
       <c r="G722" s="14"/>
     </row>
-    <row r="723" spans="1:7" s="3" customFormat="1">
+    <row r="723" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="14"/>
@@ -8025,7 +8116,7 @@
       <c r="F723" s="2"/>
       <c r="G723" s="14"/>
     </row>
-    <row r="724" spans="1:7" s="3" customFormat="1">
+    <row r="724" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="14"/>
@@ -8034,7 +8125,7 @@
       <c r="F724" s="2"/>
       <c r="G724" s="14"/>
     </row>
-    <row r="725" spans="1:7" s="3" customFormat="1">
+    <row r="725" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="14"/>
@@ -8043,7 +8134,7 @@
       <c r="F725" s="2"/>
       <c r="G725" s="14"/>
     </row>
-    <row r="726" spans="1:7" s="3" customFormat="1">
+    <row r="726" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="14"/>
@@ -8052,7 +8143,7 @@
       <c r="F726" s="2"/>
       <c r="G726" s="14"/>
     </row>
-    <row r="727" spans="1:7" s="3" customFormat="1">
+    <row r="727" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="14"/>
@@ -8061,7 +8152,7 @@
       <c r="F727" s="2"/>
       <c r="G727" s="14"/>
     </row>
-    <row r="728" spans="1:7" s="3" customFormat="1">
+    <row r="728" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="14"/>
@@ -8070,7 +8161,7 @@
       <c r="F728" s="2"/>
       <c r="G728" s="14"/>
     </row>
-    <row r="729" spans="1:7" s="3" customFormat="1">
+    <row r="729" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="14"/>
@@ -8079,7 +8170,7 @@
       <c r="F729" s="2"/>
       <c r="G729" s="14"/>
     </row>
-    <row r="730" spans="1:7" s="3" customFormat="1">
+    <row r="730" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="14"/>
@@ -8088,7 +8179,7 @@
       <c r="F730" s="2"/>
       <c r="G730" s="14"/>
     </row>
-    <row r="731" spans="1:7" s="3" customFormat="1">
+    <row r="731" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="14"/>
@@ -8097,7 +8188,7 @@
       <c r="F731" s="2"/>
       <c r="G731" s="14"/>
     </row>
-    <row r="732" spans="1:7" s="3" customFormat="1">
+    <row r="732" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="14"/>
@@ -8106,7 +8197,7 @@
       <c r="F732" s="2"/>
       <c r="G732" s="14"/>
     </row>
-    <row r="733" spans="1:7" s="3" customFormat="1">
+    <row r="733" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="14"/>
@@ -8115,7 +8206,7 @@
       <c r="F733" s="2"/>
       <c r="G733" s="14"/>
     </row>
-    <row r="734" spans="1:7" s="3" customFormat="1">
+    <row r="734" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="14"/>
@@ -8124,7 +8215,7 @@
       <c r="F734" s="2"/>
       <c r="G734" s="14"/>
     </row>
-    <row r="735" spans="1:7" s="3" customFormat="1">
+    <row r="735" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="14"/>
@@ -8133,7 +8224,7 @@
       <c r="F735" s="2"/>
       <c r="G735" s="14"/>
     </row>
-    <row r="736" spans="1:7" s="3" customFormat="1">
+    <row r="736" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="14"/>
@@ -8142,7 +8233,7 @@
       <c r="F736" s="2"/>
       <c r="G736" s="14"/>
     </row>
-    <row r="737" spans="1:7" s="3" customFormat="1">
+    <row r="737" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="14"/>
@@ -8151,7 +8242,7 @@
       <c r="F737" s="2"/>
       <c r="G737" s="14"/>
     </row>
-    <row r="738" spans="1:7" s="3" customFormat="1">
+    <row r="738" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="14"/>
@@ -8160,7 +8251,7 @@
       <c r="F738" s="2"/>
       <c r="G738" s="14"/>
     </row>
-    <row r="739" spans="1:7" s="3" customFormat="1">
+    <row r="739" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="14"/>
@@ -8169,7 +8260,7 @@
       <c r="F739" s="2"/>
       <c r="G739" s="14"/>
     </row>
-    <row r="740" spans="1:7" s="3" customFormat="1">
+    <row r="740" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="14"/>
@@ -8178,7 +8269,7 @@
       <c r="F740" s="2"/>
       <c r="G740" s="14"/>
     </row>
-    <row r="741" spans="1:7" s="3" customFormat="1">
+    <row r="741" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="14"/>
@@ -8187,7 +8278,7 @@
       <c r="F741" s="2"/>
       <c r="G741" s="14"/>
     </row>
-    <row r="742" spans="1:7" s="3" customFormat="1">
+    <row r="742" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="14"/>
@@ -8205,12 +8296,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="2ff520b0-958e-4320-8f2c-d082d148524f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8390,21 +8480,52 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="2ff520b0-958e-4320-8f2c-d082d148524f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8F1136E-1B4C-4621-97D0-E46B1551C8D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF67D73D-194A-4B75-9691-5AA77B0A4847}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="2ff520b0-958e-4320-8f2c-d082d148524f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF39B0E1-6454-4315-891A-EDDDD90BFC7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF39B0E1-6454-4315-891A-EDDDD90BFC7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2ff520b0-958e-4320-8f2c-d082d148524f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF67D73D-194A-4B75-9691-5AA77B0A4847}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8F1136E-1B4C-4621-97D0-E46B1551C8D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>